--- a/research/traditional_assets/database/data/france/france_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/france/france_healthcare_support_services.xlsx
@@ -1145,13 +1145,13 @@
         <v>182</v>
       </c>
       <c r="L2">
-        <v>378.724508850818</v>
+        <v>378.724508850819</v>
       </c>
       <c r="M2">
         <v>594.6</v>
       </c>
       <c r="N2">
-        <v>576.588508850818</v>
+        <v>576.588508850819</v>
       </c>
       <c r="O2">
         <v>437.9</v>
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08807574435978699</v>
+        <v>0.08788930499888753</v>
       </c>
       <c r="C2">
-        <v>558.8612790939198</v>
+        <v>554.050362927526</v>
       </c>
       <c r="D2">
-        <v>533.5612790939199</v>
+        <v>534.949362927526</v>
       </c>
       <c r="E2">
-        <v>-437.9</v>
+        <v>-431.701</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.199</v>
       </c>
       <c r="G2">
         <v>25.3</v>
@@ -1445,28 +1445,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3118097</v>
       </c>
       <c r="N2">
-        <v>56.09999999999999</v>
+        <v>55.7881903</v>
       </c>
       <c r="O2">
-        <v>14.025</v>
+        <v>13.947047575</v>
       </c>
       <c r="P2">
-        <v>42.075</v>
+        <v>41.841142725</v>
       </c>
       <c r="Q2">
-        <v>109.975</v>
+        <v>109.741142725</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08807574435978699</v>
+        <v>0.08839601515039144</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738457</v>
+        <v>0.8302756192024355</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>179.917430407072</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08788930499888753</v>
+        <v>0.08770286563798807</v>
       </c>
       <c r="C3">
-        <v>554.050362927526</v>
+        <v>549.2466879252729</v>
       </c>
       <c r="D3">
-        <v>534.949362927526</v>
+        <v>536.344687925273</v>
       </c>
       <c r="E3">
-        <v>-431.701</v>
+        <v>-425.502</v>
       </c>
       <c r="F3">
-        <v>6.199</v>
+        <v>12.398</v>
       </c>
       <c r="G3">
         <v>25.3</v>
@@ -1527,28 +1527,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M3">
-        <v>0.3118097</v>
+        <v>0.6236193999999999</v>
       </c>
       <c r="N3">
-        <v>55.7881903</v>
+        <v>55.47638059999999</v>
       </c>
       <c r="O3">
-        <v>13.947047575</v>
+        <v>13.86909515</v>
       </c>
       <c r="P3">
-        <v>41.841142725</v>
+        <v>41.60728544999999</v>
       </c>
       <c r="Q3">
-        <v>109.741142725</v>
+        <v>109.50728545</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08839601515039144</v>
+        <v>0.08872282207957966</v>
       </c>
       <c r="T3">
-        <v>0.8302756192024355</v>
+        <v>0.8366456945377312</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>179.917430407072</v>
+        <v>89.958715203536</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08770286563798807</v>
+        <v>0.08751642627708858</v>
       </c>
       <c r="C4">
-        <v>549.2466879252729</v>
+        <v>544.4503108973992</v>
       </c>
       <c r="D4">
-        <v>536.344687925273</v>
+        <v>537.7473108973992</v>
       </c>
       <c r="E4">
-        <v>-425.502</v>
+        <v>-419.303</v>
       </c>
       <c r="F4">
-        <v>12.398</v>
+        <v>18.597</v>
       </c>
       <c r="G4">
         <v>25.3</v>
@@ -1609,28 +1609,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M4">
-        <v>0.6236193999999999</v>
+        <v>0.9354290999999998</v>
       </c>
       <c r="N4">
-        <v>55.47638059999999</v>
+        <v>55.16457089999999</v>
       </c>
       <c r="O4">
-        <v>13.86909515</v>
+        <v>13.791142725</v>
       </c>
       <c r="P4">
-        <v>41.60728544999999</v>
+        <v>41.37342817499999</v>
       </c>
       <c r="Q4">
-        <v>109.50728545</v>
+        <v>109.273428175</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08872282207957966</v>
+        <v>0.08905636729596761</v>
       </c>
       <c r="T4">
-        <v>0.8366456945377312</v>
+        <v>0.8431471116325173</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>89.958715203536</v>
+        <v>59.97247680235734</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08751642627708858</v>
+        <v>0.08732998691618912</v>
       </c>
       <c r="C5">
-        <v>544.4503108973992</v>
+        <v>539.6612892499703</v>
       </c>
       <c r="D5">
-        <v>537.7473108973992</v>
+        <v>539.1572892499704</v>
       </c>
       <c r="E5">
-        <v>-419.303</v>
+        <v>-413.104</v>
       </c>
       <c r="F5">
-        <v>18.597</v>
+        <v>24.796</v>
       </c>
       <c r="G5">
         <v>25.3</v>
@@ -1691,28 +1691,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M5">
-        <v>0.9354290999999998</v>
+        <v>1.2472388</v>
       </c>
       <c r="N5">
-        <v>55.16457089999999</v>
+        <v>54.8527612</v>
       </c>
       <c r="O5">
-        <v>13.791142725</v>
+        <v>13.7131903</v>
       </c>
       <c r="P5">
-        <v>41.37342817499999</v>
+        <v>41.1395709</v>
       </c>
       <c r="Q5">
-        <v>109.273428175</v>
+        <v>109.0395709</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08905636729596761</v>
+        <v>0.08939686137103034</v>
       </c>
       <c r="T5">
-        <v>0.8431471116325173</v>
+        <v>0.8497839749167784</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.97247680235734</v>
+        <v>44.979357601768</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08732998691618912</v>
+        <v>0.08714354755528966</v>
       </c>
       <c r="C6">
-        <v>539.6612892499703</v>
+        <v>534.8796809927126</v>
       </c>
       <c r="D6">
-        <v>539.1572892499704</v>
+        <v>540.5746809927126</v>
       </c>
       <c r="E6">
-        <v>-413.104</v>
+        <v>-406.905</v>
       </c>
       <c r="F6">
-        <v>24.796</v>
+        <v>30.995</v>
       </c>
       <c r="G6">
         <v>25.3</v>
@@ -1773,28 +1773,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M6">
-        <v>1.2472388</v>
+        <v>1.5590485</v>
       </c>
       <c r="N6">
-        <v>54.8527612</v>
+        <v>54.54095149999999</v>
       </c>
       <c r="O6">
-        <v>13.7131903</v>
+        <v>13.635237875</v>
       </c>
       <c r="P6">
-        <v>41.1395709</v>
+        <v>40.90571362499999</v>
       </c>
       <c r="Q6">
-        <v>109.0395709</v>
+        <v>108.805713625</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08939686137103034</v>
+        <v>0.08974452374241017</v>
       </c>
       <c r="T6">
-        <v>0.8497839749167784</v>
+        <v>0.8565605616386028</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.979357601768</v>
+        <v>35.98348608141439</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08714354755528966</v>
+        <v>0.08695710819439019</v>
       </c>
       <c r="C7">
-        <v>534.8796809927126</v>
+        <v>530.1055447469672</v>
       </c>
       <c r="D7">
-        <v>540.5746809927126</v>
+        <v>541.9995447469672</v>
       </c>
       <c r="E7">
-        <v>-406.905</v>
+        <v>-400.706</v>
       </c>
       <c r="F7">
-        <v>30.995</v>
+        <v>37.194</v>
       </c>
       <c r="G7">
         <v>25.3</v>
@@ -1855,28 +1855,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M7">
-        <v>1.5590485</v>
+        <v>1.8708582</v>
       </c>
       <c r="N7">
-        <v>54.54095149999999</v>
+        <v>54.22914179999999</v>
       </c>
       <c r="O7">
-        <v>13.635237875</v>
+        <v>13.55728545</v>
       </c>
       <c r="P7">
-        <v>40.90571362499999</v>
+        <v>40.67185635</v>
       </c>
       <c r="Q7">
-        <v>108.805713625</v>
+        <v>108.57185635</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08974452374241017</v>
+        <v>0.09009958318552148</v>
       </c>
       <c r="T7">
-        <v>0.8565605616386028</v>
+        <v>0.8634813310566363</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.98348608141439</v>
+        <v>29.98623840117866</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08695710819439019</v>
+        <v>0.08677066883349073</v>
       </c>
       <c r="C8">
-        <v>530.1055447469672</v>
+        <v>525.3389397537725</v>
       </c>
       <c r="D8">
-        <v>541.9995447469672</v>
+        <v>543.4319397537726</v>
       </c>
       <c r="E8">
-        <v>-400.706</v>
+        <v>-394.507</v>
       </c>
       <c r="F8">
-        <v>37.194</v>
+        <v>43.39299999999999</v>
       </c>
       <c r="G8">
         <v>25.3</v>
@@ -1937,28 +1937,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M8">
-        <v>1.8708582</v>
+        <v>2.1826679</v>
       </c>
       <c r="N8">
-        <v>54.22914179999999</v>
+        <v>53.9173321</v>
       </c>
       <c r="O8">
-        <v>13.55728545</v>
+        <v>13.479333025</v>
       </c>
       <c r="P8">
-        <v>40.67185635</v>
+        <v>40.43799907499999</v>
       </c>
       <c r="Q8">
-        <v>108.57185635</v>
+        <v>108.337999075</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09009958318552148</v>
+        <v>0.09046227831558143</v>
       </c>
       <c r="T8">
-        <v>0.8634813310566363</v>
+        <v>0.870550934225595</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.98623840117867</v>
+        <v>25.70249005815315</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08677066883349072</v>
+        <v>0.08658422947259128</v>
       </c>
       <c r="C9">
-        <v>525.3389397537726</v>
+        <v>520.579925882075</v>
       </c>
       <c r="D9">
-        <v>543.4319397537727</v>
+        <v>544.8719258820751</v>
       </c>
       <c r="E9">
-        <v>-394.5069999999999</v>
+        <v>-388.308</v>
       </c>
       <c r="F9">
-        <v>43.393</v>
+        <v>49.592</v>
       </c>
       <c r="G9">
         <v>25.3</v>
@@ -2019,28 +2019,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M9">
-        <v>2.1826679</v>
+        <v>2.4944776</v>
       </c>
       <c r="N9">
-        <v>53.9173321</v>
+        <v>53.6055224</v>
       </c>
       <c r="O9">
-        <v>13.479333025</v>
+        <v>13.4013806</v>
       </c>
       <c r="P9">
-        <v>40.43799907499999</v>
+        <v>40.2041418</v>
       </c>
       <c r="Q9">
-        <v>108.337999075</v>
+        <v>108.1041418</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09046227831558143</v>
+        <v>0.09083285812238182</v>
       </c>
       <c r="T9">
-        <v>0.870550934225595</v>
+        <v>0.8777742244199662</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.70249005815315</v>
+        <v>22.489678800884</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08658422947259128</v>
+        <v>0.0863977901116918</v>
       </c>
       <c r="C10">
-        <v>520.579925882075</v>
+        <v>515.8285636370701</v>
       </c>
       <c r="D10">
-        <v>544.8719258820751</v>
+        <v>546.3195636370701</v>
       </c>
       <c r="E10">
-        <v>-388.308</v>
+        <v>-382.109</v>
       </c>
       <c r="F10">
-        <v>49.592</v>
+        <v>55.791</v>
       </c>
       <c r="G10">
         <v>25.3</v>
@@ -2101,28 +2101,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M10">
-        <v>2.4944776</v>
+        <v>2.8062873</v>
       </c>
       <c r="N10">
-        <v>53.6055224</v>
+        <v>53.29371269999999</v>
       </c>
       <c r="O10">
-        <v>13.4013806</v>
+        <v>13.323428175</v>
       </c>
       <c r="P10">
-        <v>40.2041418</v>
+        <v>39.970284525</v>
       </c>
       <c r="Q10">
-        <v>108.1041418</v>
+        <v>107.870284525</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09083285812238182</v>
+        <v>0.09121158254032065</v>
       </c>
       <c r="T10">
-        <v>0.8777742244199662</v>
+        <v>0.8851562682449826</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.489678800884</v>
+        <v>19.99082560078578</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0863977901116918</v>
+        <v>0.08621135075079231</v>
       </c>
       <c r="C11">
-        <v>515.8285636370701</v>
+        <v>511.0849141686763</v>
       </c>
       <c r="D11">
-        <v>546.3195636370701</v>
+        <v>547.7749141686763</v>
       </c>
       <c r="E11">
-        <v>-382.109</v>
+        <v>-375.91</v>
       </c>
       <c r="F11">
-        <v>55.791</v>
+        <v>61.98999999999999</v>
       </c>
       <c r="G11">
         <v>25.3</v>
@@ -2183,28 +2183,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M11">
-        <v>2.8062873</v>
+        <v>3.118097</v>
       </c>
       <c r="N11">
-        <v>53.29371269999999</v>
+        <v>52.981903</v>
       </c>
       <c r="O11">
-        <v>13.323428175</v>
+        <v>13.24547575</v>
       </c>
       <c r="P11">
-        <v>39.970284525</v>
+        <v>39.73642725</v>
       </c>
       <c r="Q11">
-        <v>107.870284525</v>
+        <v>107.63642725</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09121158254032065</v>
+        <v>0.0915987230564359</v>
       </c>
       <c r="T11">
-        <v>0.8851562682449826</v>
+        <v>0.8927023574883328</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.99082560078578</v>
+        <v>17.9917430407072</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08621135075079231</v>
+        <v>0.08602491138989285</v>
       </c>
       <c r="C12">
-        <v>511.0849141686763</v>
+        <v>506.3490392801461</v>
       </c>
       <c r="D12">
-        <v>547.7749141686763</v>
+        <v>549.2380392801462</v>
       </c>
       <c r="E12">
-        <v>-375.91</v>
+        <v>-369.711</v>
       </c>
       <c r="F12">
-        <v>61.99</v>
+        <v>68.18899999999999</v>
       </c>
       <c r="G12">
         <v>25.3</v>
@@ -2265,28 +2265,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M12">
-        <v>3.118097</v>
+        <v>3.4299067</v>
       </c>
       <c r="N12">
-        <v>52.981903</v>
+        <v>52.6700933</v>
       </c>
       <c r="O12">
-        <v>13.24547575</v>
+        <v>13.167523325</v>
       </c>
       <c r="P12">
-        <v>39.73642725</v>
+        <v>39.502569975</v>
       </c>
       <c r="Q12">
-        <v>107.63642725</v>
+        <v>107.402569975</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0915987230564359</v>
+        <v>0.09199456335943018</v>
       </c>
       <c r="T12">
-        <v>0.8927023574883328</v>
+        <v>0.9004180217708596</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.9917430407072</v>
+        <v>16.35613003700655</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08602491138989285</v>
+        <v>0.08583847202899339</v>
       </c>
       <c r="C13">
-        <v>506.3490392801461</v>
+        <v>501.6210014368149</v>
       </c>
       <c r="D13">
-        <v>549.2380392801462</v>
+        <v>550.7090014368149</v>
       </c>
       <c r="E13">
-        <v>-369.711</v>
+        <v>-363.512</v>
       </c>
       <c r="F13">
-        <v>68.18899999999999</v>
+        <v>74.38799999999999</v>
       </c>
       <c r="G13">
         <v>25.3</v>
@@ -2347,28 +2347,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M13">
-        <v>3.4299067</v>
+        <v>3.741716399999999</v>
       </c>
       <c r="N13">
-        <v>52.6700933</v>
+        <v>52.35828359999999</v>
       </c>
       <c r="O13">
-        <v>13.167523325</v>
+        <v>13.0895709</v>
       </c>
       <c r="P13">
-        <v>39.502569975</v>
+        <v>39.26871269999999</v>
       </c>
       <c r="Q13">
-        <v>107.402569975</v>
+        <v>107.1687127</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09199456335943018</v>
+        <v>0.09239940003294703</v>
       </c>
       <c r="T13">
-        <v>0.9004180217708596</v>
+        <v>0.9083090420598072</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.35613003700655</v>
+        <v>14.99311920058934</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08583847202899339</v>
+        <v>0.0856520326680939</v>
       </c>
       <c r="C14">
-        <v>501.6210014368149</v>
+        <v>496.9008637749907</v>
       </c>
       <c r="D14">
-        <v>550.7090014368149</v>
+        <v>552.1878637749908</v>
       </c>
       <c r="E14">
-        <v>-363.512</v>
+        <v>-357.313</v>
       </c>
       <c r="F14">
-        <v>74.38799999999999</v>
+        <v>80.587</v>
       </c>
       <c r="G14">
         <v>25.3</v>
@@ -2429,28 +2429,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M14">
-        <v>3.741716399999999</v>
+        <v>4.0535261</v>
       </c>
       <c r="N14">
-        <v>52.35828359999999</v>
+        <v>52.0464739</v>
       </c>
       <c r="O14">
-        <v>13.0895709</v>
+        <v>13.011618475</v>
       </c>
       <c r="P14">
-        <v>39.26871269999999</v>
+        <v>39.034855425</v>
       </c>
       <c r="Q14">
-        <v>107.1687127</v>
+        <v>106.934855425</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09239940003294703</v>
+        <v>0.09281354329665967</v>
       </c>
       <c r="T14">
-        <v>0.9083090420598072</v>
+        <v>0.9163814651140181</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.99311920058934</v>
+        <v>13.83980233900554</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0856520326680939</v>
+        <v>0.08562309330719445</v>
       </c>
       <c r="C15">
-        <v>496.9008637749907</v>
+        <v>490.932127128492</v>
       </c>
       <c r="D15">
-        <v>552.1878637749908</v>
+        <v>552.4181271284921</v>
       </c>
       <c r="E15">
-        <v>-357.313</v>
+        <v>-351.114</v>
       </c>
       <c r="F15">
-        <v>80.587</v>
+        <v>86.786</v>
       </c>
       <c r="G15">
         <v>25.3</v>
@@ -2511,45 +2511,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M15">
-        <v>4.0535261</v>
+        <v>4.4955148</v>
       </c>
       <c r="N15">
-        <v>52.0464739</v>
+        <v>51.60448519999999</v>
       </c>
       <c r="O15">
-        <v>13.011618475</v>
+        <v>12.9011213</v>
       </c>
       <c r="P15">
-        <v>39.034855425</v>
+        <v>38.70336389999999</v>
       </c>
       <c r="Q15">
-        <v>106.934855425</v>
+        <v>106.6033639</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09281354329665967</v>
+        <v>0.09323731779906332</v>
       </c>
       <c r="T15">
-        <v>0.9163814651140181</v>
+        <v>0.9246416189369315</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.83980233900554</v>
+        <v>12.47910472900679</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08562309330719445</v>
+        <v>0.08544790394629498</v>
       </c>
       <c r="C16">
-        <v>490.932127128492</v>
+        <v>486.1311761412259</v>
       </c>
       <c r="D16">
-        <v>552.4181271284921</v>
+        <v>553.8161761412259</v>
       </c>
       <c r="E16">
-        <v>-351.114</v>
+        <v>-344.915</v>
       </c>
       <c r="F16">
-        <v>86.786</v>
+        <v>92.98500000000001</v>
       </c>
       <c r="G16">
         <v>25.3</v>
@@ -2593,28 +2593,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M16">
-        <v>4.4955148</v>
+        <v>4.816623000000001</v>
       </c>
       <c r="N16">
-        <v>51.60448519999999</v>
+        <v>51.28337699999999</v>
       </c>
       <c r="O16">
-        <v>12.9011213</v>
+        <v>12.82084425</v>
       </c>
       <c r="P16">
-        <v>38.70336389999999</v>
+        <v>38.46253274999999</v>
       </c>
       <c r="Q16">
-        <v>106.6033639</v>
+        <v>106.36253275</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09323731779906332</v>
+        <v>0.09367106346622939</v>
       </c>
       <c r="T16">
-        <v>0.9246416189369315</v>
+        <v>0.9330961293203841</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.47910472900679</v>
+        <v>11.64716441373966</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08544790394629498</v>
+        <v>0.08527271458539551</v>
       </c>
       <c r="C17">
-        <v>486.1311761412259</v>
+        <v>481.3373194182873</v>
       </c>
       <c r="D17">
-        <v>553.8161761412259</v>
+        <v>555.2213194182873</v>
       </c>
       <c r="E17">
-        <v>-344.915</v>
+        <v>-338.716</v>
       </c>
       <c r="F17">
-        <v>92.985</v>
+        <v>99.184</v>
       </c>
       <c r="G17">
         <v>25.3</v>
@@ -2675,28 +2675,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M17">
-        <v>4.816623</v>
+        <v>5.1377312</v>
       </c>
       <c r="N17">
-        <v>51.28337699999999</v>
+        <v>50.9622688</v>
       </c>
       <c r="O17">
-        <v>12.82084425</v>
+        <v>12.7405672</v>
       </c>
       <c r="P17">
-        <v>38.46253274999999</v>
+        <v>38.2217016</v>
       </c>
       <c r="Q17">
-        <v>106.36253275</v>
+        <v>106.1217016</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09367106346622939</v>
+        <v>0.09411513641118513</v>
       </c>
       <c r="T17">
-        <v>0.9330961293203841</v>
+        <v>0.9417519375701093</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.64716441373967</v>
+        <v>10.91921663788094</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08527271458539551</v>
+        <v>0.08509752522449604</v>
       </c>
       <c r="C18">
-        <v>481.3373194182873</v>
+        <v>476.5506110957665</v>
       </c>
       <c r="D18">
-        <v>555.2213194182873</v>
+        <v>556.6336110957666</v>
       </c>
       <c r="E18">
-        <v>-338.716</v>
+        <v>-332.5169999999999</v>
       </c>
       <c r="F18">
-        <v>99.184</v>
+        <v>105.383</v>
       </c>
       <c r="G18">
         <v>25.3</v>
@@ -2757,28 +2757,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M18">
-        <v>5.1377312</v>
+        <v>5.4588394</v>
       </c>
       <c r="N18">
-        <v>50.9622688</v>
+        <v>50.64116059999999</v>
       </c>
       <c r="O18">
-        <v>12.7405672</v>
+        <v>12.66029015</v>
       </c>
       <c r="P18">
-        <v>38.2217016</v>
+        <v>37.98087045</v>
       </c>
       <c r="Q18">
-        <v>106.1217016</v>
+        <v>105.88087045</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09411513641118513</v>
+        <v>0.09456990990903139</v>
       </c>
       <c r="T18">
-        <v>0.9417519375701093</v>
+        <v>0.9506163195125993</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.91921663788094</v>
+        <v>10.27690977682912</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08509752522449604</v>
+        <v>0.08515183586359658</v>
       </c>
       <c r="C19">
-        <v>476.5506110957665</v>
+        <v>469.9130172384021</v>
       </c>
       <c r="D19">
-        <v>556.6336110957666</v>
+        <v>556.1950172384021</v>
       </c>
       <c r="E19">
-        <v>-332.5169999999999</v>
+        <v>-326.318</v>
       </c>
       <c r="F19">
-        <v>105.383</v>
+        <v>111.582</v>
       </c>
       <c r="G19">
         <v>25.3</v>
@@ -2839,45 +2839,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M19">
-        <v>5.4588394</v>
+        <v>5.969637000000001</v>
       </c>
       <c r="N19">
-        <v>50.64116059999999</v>
+        <v>50.130363</v>
       </c>
       <c r="O19">
-        <v>12.66029015</v>
+        <v>12.53259075</v>
       </c>
       <c r="P19">
-        <v>37.98087045</v>
+        <v>37.59777225</v>
       </c>
       <c r="Q19">
-        <v>105.88087045</v>
+        <v>105.49777225</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09456990990903139</v>
+        <v>0.09503577544341046</v>
       </c>
       <c r="T19">
-        <v>0.9506163195125993</v>
+        <v>0.9596969058927105</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.27690977682912</v>
+        <v>9.397556333827332</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08515183586359659</v>
+        <v>0.08498939650269711</v>
       </c>
       <c r="C20">
-        <v>469.9130172384019</v>
+        <v>465.0278838284071</v>
       </c>
       <c r="D20">
-        <v>556.195017238402</v>
+        <v>557.5088838284072</v>
       </c>
       <c r="E20">
-        <v>-326.318</v>
+        <v>-320.119</v>
       </c>
       <c r="F20">
-        <v>111.582</v>
+        <v>117.781</v>
       </c>
       <c r="G20">
         <v>25.3</v>
@@ -2921,28 +2921,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M20">
-        <v>5.969637</v>
+        <v>6.301283499999999</v>
       </c>
       <c r="N20">
-        <v>50.130363</v>
+        <v>49.7987165</v>
       </c>
       <c r="O20">
-        <v>12.53259075</v>
+        <v>12.449679125</v>
       </c>
       <c r="P20">
-        <v>37.59777225</v>
+        <v>37.34903737499999</v>
       </c>
       <c r="Q20">
-        <v>105.49777225</v>
+        <v>105.249037375</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09503577544341046</v>
+        <v>0.09551314383049027</v>
       </c>
       <c r="T20">
-        <v>0.9596969058927105</v>
+        <v>0.9690017042822076</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.397556333827334</v>
+        <v>8.902948105731159</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08498939650269711</v>
+        <v>0.08482695714179767</v>
       </c>
       <c r="C21">
-        <v>465.0278838284071</v>
+        <v>460.1489724550205</v>
       </c>
       <c r="D21">
-        <v>557.5088838284072</v>
+        <v>558.8289724550206</v>
       </c>
       <c r="E21">
-        <v>-320.119</v>
+        <v>-313.92</v>
       </c>
       <c r="F21">
-        <v>117.781</v>
+        <v>123.98</v>
       </c>
       <c r="G21">
         <v>25.3</v>
@@ -3003,28 +3003,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M21">
-        <v>6.301283499999999</v>
+        <v>6.63293</v>
       </c>
       <c r="N21">
-        <v>49.7987165</v>
+        <v>49.46706999999999</v>
       </c>
       <c r="O21">
-        <v>12.449679125</v>
+        <v>12.3667675</v>
       </c>
       <c r="P21">
-        <v>37.34903737499999</v>
+        <v>37.1003025</v>
       </c>
       <c r="Q21">
-        <v>105.249037375</v>
+        <v>105.0003025</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09551314383049027</v>
+        <v>0.09600244642724706</v>
       </c>
       <c r="T21">
-        <v>0.9690017042822076</v>
+        <v>0.9785391226314418</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.902948105731159</v>
+        <v>8.457800700444599</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08482695714179767</v>
+        <v>0.08466451778089817</v>
       </c>
       <c r="C22">
-        <v>460.1489724550205</v>
+        <v>455.2763274213994</v>
       </c>
       <c r="D22">
-        <v>558.8289724550206</v>
+        <v>560.1553274213994</v>
       </c>
       <c r="E22">
-        <v>-313.92</v>
+        <v>-307.721</v>
       </c>
       <c r="F22">
-        <v>123.98</v>
+        <v>130.179</v>
       </c>
       <c r="G22">
         <v>25.3</v>
@@ -3085,28 +3085,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M22">
-        <v>6.63293</v>
+        <v>6.9645765</v>
       </c>
       <c r="N22">
-        <v>49.46706999999999</v>
+        <v>49.13542349999999</v>
       </c>
       <c r="O22">
-        <v>12.3667675</v>
+        <v>12.283855875</v>
       </c>
       <c r="P22">
-        <v>37.1003025</v>
+        <v>36.85156762499999</v>
       </c>
       <c r="Q22">
-        <v>105.0003025</v>
+        <v>104.751567625</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09600244642724706</v>
+        <v>0.09650413643151667</v>
       </c>
       <c r="T22">
-        <v>0.9785391226314418</v>
+        <v>0.9883179946097707</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.457800700444599</v>
+        <v>8.055048286137714</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08466451778089817</v>
+        <v>0.08450207841999871</v>
       </c>
       <c r="C23">
-        <v>455.2763274213994</v>
+        <v>450.4099934523063</v>
       </c>
       <c r="D23">
-        <v>560.1553274213994</v>
+        <v>561.4879934523063</v>
       </c>
       <c r="E23">
-        <v>-307.721</v>
+        <v>-301.522</v>
       </c>
       <c r="F23">
-        <v>130.179</v>
+        <v>136.378</v>
       </c>
       <c r="G23">
         <v>25.3</v>
@@ -3167,28 +3167,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M23">
-        <v>6.9645765</v>
+        <v>7.296222999999999</v>
       </c>
       <c r="N23">
-        <v>49.13542349999999</v>
+        <v>48.803777</v>
       </c>
       <c r="O23">
-        <v>12.283855875</v>
+        <v>12.20094425</v>
       </c>
       <c r="P23">
-        <v>36.85156762499999</v>
+        <v>36.60283275</v>
       </c>
       <c r="Q23">
-        <v>104.751567625</v>
+        <v>104.50283275</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09650413643151667</v>
+        <v>0.09701869028204962</v>
       </c>
       <c r="T23">
-        <v>0.9883179946097707</v>
+        <v>0.9983476068952362</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.055048286137714</v>
+        <v>7.688909727676909</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08450207841999871</v>
+        <v>0.08447763905909925</v>
       </c>
       <c r="C24">
-        <v>450.4099934523063</v>
+        <v>444.4120449827255</v>
       </c>
       <c r="D24">
-        <v>561.4879934523063</v>
+        <v>561.6890449827256</v>
       </c>
       <c r="E24">
-        <v>-301.522</v>
+        <v>-295.323</v>
       </c>
       <c r="F24">
-        <v>136.378</v>
+        <v>142.577</v>
       </c>
       <c r="G24">
         <v>25.3</v>
@@ -3249,45 +3249,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M24">
-        <v>7.296222999999999</v>
+        <v>7.7419311</v>
       </c>
       <c r="N24">
-        <v>48.803777</v>
+        <v>48.35806889999999</v>
       </c>
       <c r="O24">
-        <v>12.20094425</v>
+        <v>12.089517225</v>
       </c>
       <c r="P24">
-        <v>36.60283275</v>
+        <v>36.268551675</v>
       </c>
       <c r="Q24">
-        <v>104.50283275</v>
+        <v>104.168551675</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09701869028204962</v>
+        <v>0.09754660916766136</v>
       </c>
       <c r="T24">
-        <v>0.9983476068952362</v>
+        <v>1.008637728590714</v>
       </c>
       <c r="U24">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.688909727676909</v>
+        <v>7.246254103191385</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08447763905909925</v>
+        <v>0.08432119969819979</v>
       </c>
       <c r="C25">
-        <v>444.4120449827255</v>
+        <v>439.5034190196849</v>
       </c>
       <c r="D25">
-        <v>561.6890449827256</v>
+        <v>562.979419019685</v>
       </c>
       <c r="E25">
-        <v>-295.323</v>
+        <v>-289.124</v>
       </c>
       <c r="F25">
-        <v>142.577</v>
+        <v>148.776</v>
       </c>
       <c r="G25">
         <v>25.3</v>
@@ -3331,28 +3331,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M25">
-        <v>7.7419311</v>
+        <v>8.0785368</v>
       </c>
       <c r="N25">
-        <v>48.35806889999999</v>
+        <v>48.02146319999999</v>
       </c>
       <c r="O25">
-        <v>12.089517225</v>
+        <v>12.0053658</v>
       </c>
       <c r="P25">
-        <v>36.268551675</v>
+        <v>36.01609739999999</v>
       </c>
       <c r="Q25">
-        <v>104.168551675</v>
+        <v>103.9160974</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09754660916766136</v>
+        <v>0.09808842065552603</v>
       </c>
       <c r="T25">
-        <v>1.008637728590714</v>
+        <v>1.019198642962388</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.246254103191385</v>
+        <v>6.944326848891744</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08432119969819979</v>
+        <v>0.08416476033730032</v>
       </c>
       <c r="C26">
-        <v>439.503419019685</v>
+        <v>434.6007354874229</v>
       </c>
       <c r="D26">
-        <v>562.979419019685</v>
+        <v>564.2757354874229</v>
       </c>
       <c r="E26">
-        <v>-289.124</v>
+        <v>-282.925</v>
       </c>
       <c r="F26">
-        <v>148.776</v>
+        <v>154.975</v>
       </c>
       <c r="G26">
         <v>25.3</v>
@@ -3413,28 +3413,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M26">
-        <v>8.078536799999998</v>
+        <v>8.4151425</v>
       </c>
       <c r="N26">
-        <v>48.0214632</v>
+        <v>47.68485749999999</v>
       </c>
       <c r="O26">
-        <v>12.0053658</v>
+        <v>11.921214375</v>
       </c>
       <c r="P26">
-        <v>36.0160974</v>
+        <v>35.76364312499999</v>
       </c>
       <c r="Q26">
-        <v>103.9160974</v>
+        <v>103.663643125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09808842065552603</v>
+        <v>0.09864468044973375</v>
       </c>
       <c r="T26">
-        <v>1.019198642962388</v>
+        <v>1.030041181717307</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.944326848891746</v>
+        <v>6.666553774936074</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08416476033730032</v>
+        <v>0.08400832097640085</v>
       </c>
       <c r="C27">
-        <v>434.6007354874229</v>
+        <v>429.7040355298026</v>
       </c>
       <c r="D27">
-        <v>564.2757354874229</v>
+        <v>565.5780355298026</v>
       </c>
       <c r="E27">
-        <v>-282.925</v>
+        <v>-276.726</v>
       </c>
       <c r="F27">
-        <v>154.975</v>
+        <v>161.174</v>
       </c>
       <c r="G27">
         <v>25.3</v>
@@ -3495,28 +3495,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M27">
-        <v>8.4151425</v>
+        <v>8.7517482</v>
       </c>
       <c r="N27">
-        <v>47.68485749999999</v>
+        <v>47.34825179999999</v>
       </c>
       <c r="O27">
-        <v>11.921214375</v>
+        <v>11.83706295</v>
       </c>
       <c r="P27">
-        <v>35.76364312499999</v>
+        <v>35.51118885</v>
       </c>
       <c r="Q27">
-        <v>103.663643125</v>
+        <v>103.41118885</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09864468044973375</v>
+        <v>0.09921597429243358</v>
       </c>
       <c r="T27">
-        <v>1.030041181717307</v>
+        <v>1.041176762060197</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.666553774936074</v>
+        <v>6.410147860515456</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08400832097640085</v>
+        <v>0.08385188161550138</v>
       </c>
       <c r="C28">
-        <v>429.7040355298026</v>
+        <v>424.8133606713914</v>
       </c>
       <c r="D28">
-        <v>565.5780355298026</v>
+        <v>566.8863606713915</v>
       </c>
       <c r="E28">
-        <v>-276.726</v>
+        <v>-270.5269999999999</v>
       </c>
       <c r="F28">
-        <v>161.174</v>
+        <v>167.373</v>
       </c>
       <c r="G28">
         <v>25.3</v>
@@ -3577,28 +3577,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M28">
-        <v>8.7517482</v>
+        <v>9.088353900000001</v>
       </c>
       <c r="N28">
-        <v>47.34825179999999</v>
+        <v>47.01164609999999</v>
       </c>
       <c r="O28">
-        <v>11.83706295</v>
+        <v>11.752911525</v>
       </c>
       <c r="P28">
-        <v>35.51118885</v>
+        <v>35.25873457499999</v>
       </c>
       <c r="Q28">
-        <v>103.41118885</v>
+        <v>103.158734575</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09921597429243358</v>
+        <v>0.09980292002123477</v>
       </c>
       <c r="T28">
-        <v>1.041176762060197</v>
+        <v>1.052617426796043</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.410147860515456</v>
+        <v>6.17273497679266</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08385188161550138</v>
+        <v>0.08390544225460191</v>
       </c>
       <c r="C29">
-        <v>424.8133606713914</v>
+        <v>418.1657443662203</v>
       </c>
       <c r="D29">
-        <v>566.8863606713915</v>
+        <v>566.4377443662204</v>
       </c>
       <c r="E29">
-        <v>-270.5269999999999</v>
+        <v>-264.328</v>
       </c>
       <c r="F29">
-        <v>167.373</v>
+        <v>173.572</v>
       </c>
       <c r="G29">
         <v>25.3</v>
@@ -3659,45 +3659,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M29">
-        <v>9.088353900000001</v>
+        <v>9.598531600000001</v>
       </c>
       <c r="N29">
-        <v>47.01164609999999</v>
+        <v>46.50146839999999</v>
       </c>
       <c r="O29">
-        <v>11.752911525</v>
+        <v>11.6253671</v>
       </c>
       <c r="P29">
-        <v>35.25873457499999</v>
+        <v>34.87610129999999</v>
       </c>
       <c r="Q29">
-        <v>103.158734575</v>
+        <v>102.7761013</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09980292002123477</v>
+        <v>0.1004061697980582</v>
       </c>
       <c r="T29">
-        <v>1.052617426796043</v>
+        <v>1.064375887774551</v>
       </c>
       <c r="U29">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.17273497679266</v>
+        <v>5.844643987003177</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08390544225460191</v>
+        <v>0.08375650289370243</v>
       </c>
       <c r="C30">
-        <v>418.1657443662203</v>
+        <v>413.2160011935826</v>
       </c>
       <c r="D30">
-        <v>566.4377443662204</v>
+        <v>567.6870011935827</v>
       </c>
       <c r="E30">
-        <v>-264.328</v>
+        <v>-258.129</v>
       </c>
       <c r="F30">
-        <v>173.572</v>
+        <v>179.771</v>
       </c>
       <c r="G30">
         <v>25.3</v>
@@ -3741,28 +3741,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M30">
-        <v>9.598531600000001</v>
+        <v>9.941336300000001</v>
       </c>
       <c r="N30">
-        <v>46.50146839999999</v>
+        <v>46.15866369999999</v>
       </c>
       <c r="O30">
-        <v>11.6253671</v>
+        <v>11.539665925</v>
       </c>
       <c r="P30">
-        <v>34.87610129999999</v>
+        <v>34.618997775</v>
       </c>
       <c r="Q30">
-        <v>102.7761013</v>
+        <v>102.518997775</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1004061697980582</v>
+        <v>0.1010264125263415</v>
       </c>
       <c r="T30">
-        <v>1.064375887774551</v>
+        <v>1.076465573005974</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.844643987003177</v>
+        <v>5.643104539175481</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08375650289370243</v>
+        <v>0.08360756353280296</v>
       </c>
       <c r="C31">
-        <v>413.2160011935827</v>
+        <v>408.2717805772428</v>
       </c>
       <c r="D31">
-        <v>567.6870011935827</v>
+        <v>568.9417805772429</v>
       </c>
       <c r="E31">
-        <v>-258.129</v>
+        <v>-251.93</v>
       </c>
       <c r="F31">
-        <v>179.771</v>
+        <v>185.97</v>
       </c>
       <c r="G31">
         <v>25.3</v>
@@ -3823,28 +3823,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M31">
-        <v>9.9413363</v>
+        <v>10.284141</v>
       </c>
       <c r="N31">
-        <v>46.15866369999999</v>
+        <v>45.815859</v>
       </c>
       <c r="O31">
-        <v>11.539665925</v>
+        <v>11.45396475</v>
       </c>
       <c r="P31">
-        <v>34.618997775</v>
+        <v>34.36189425</v>
       </c>
       <c r="Q31">
-        <v>102.518997775</v>
+        <v>102.26189425</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1010264125263415</v>
+        <v>0.1016643764754328</v>
       </c>
       <c r="T31">
-        <v>1.076465573005974</v>
+        <v>1.088900677815439</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.643104539175482</v>
+        <v>5.4550010545363</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08360756353280296</v>
+        <v>0.0834586241719035</v>
       </c>
       <c r="C32">
-        <v>408.2717805772428</v>
+        <v>403.3331192184489</v>
       </c>
       <c r="D32">
-        <v>568.9417805772429</v>
+        <v>570.202119218449</v>
       </c>
       <c r="E32">
-        <v>-251.93</v>
+        <v>-245.731</v>
       </c>
       <c r="F32">
-        <v>185.97</v>
+        <v>192.169</v>
       </c>
       <c r="G32">
         <v>25.3</v>
@@ -3905,28 +3905,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M32">
-        <v>10.284141</v>
+        <v>10.6269457</v>
       </c>
       <c r="N32">
-        <v>45.815859</v>
+        <v>45.47305429999999</v>
       </c>
       <c r="O32">
-        <v>11.45396475</v>
+        <v>11.368263575</v>
       </c>
       <c r="P32">
-        <v>34.36189425</v>
+        <v>34.10479072499999</v>
       </c>
       <c r="Q32">
-        <v>102.26189425</v>
+        <v>102.004790725</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1016643764754328</v>
+        <v>0.1023208321331935</v>
       </c>
       <c r="T32">
-        <v>1.088900677815439</v>
+        <v>1.101696220445468</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.4550010545363</v>
+        <v>5.279033278583515</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.0834586241719035</v>
+        <v>0.08330968481100404</v>
       </c>
       <c r="C33">
-        <v>403.3331192184489</v>
+        <v>398.400054144378</v>
       </c>
       <c r="D33">
-        <v>570.202119218449</v>
+        <v>571.468054144378</v>
       </c>
       <c r="E33">
-        <v>-245.731</v>
+        <v>-239.532</v>
       </c>
       <c r="F33">
-        <v>192.169</v>
+        <v>198.368</v>
       </c>
       <c r="G33">
         <v>25.3</v>
@@ -3987,28 +3987,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M33">
-        <v>10.6269457</v>
+        <v>10.9697504</v>
       </c>
       <c r="N33">
-        <v>45.47305429999999</v>
+        <v>45.13024959999999</v>
       </c>
       <c r="O33">
-        <v>11.368263575</v>
+        <v>11.2825624</v>
       </c>
       <c r="P33">
-        <v>34.10479072499999</v>
+        <v>33.8476872</v>
       </c>
       <c r="Q33">
-        <v>102.004790725</v>
+        <v>101.7476872</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1023208321331935</v>
+        <v>0.1029965953103001</v>
       </c>
       <c r="T33">
-        <v>1.101696220445468</v>
+        <v>1.114868102564615</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.279033278583515</v>
+        <v>5.114063488627781</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08330968481100404</v>
+        <v>0.08316074545010456</v>
       </c>
       <c r="C34">
-        <v>398.400054144378</v>
+        <v>393.4726227117626</v>
       </c>
       <c r="D34">
-        <v>571.468054144378</v>
+        <v>572.7396227117626</v>
       </c>
       <c r="E34">
-        <v>-239.532</v>
+        <v>-233.333</v>
       </c>
       <c r="F34">
-        <v>198.368</v>
+        <v>204.567</v>
       </c>
       <c r="G34">
         <v>25.3</v>
@@ -4069,28 +4069,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M34">
-        <v>10.9697504</v>
+        <v>11.3125551</v>
       </c>
       <c r="N34">
-        <v>45.13024959999999</v>
+        <v>44.7874449</v>
       </c>
       <c r="O34">
-        <v>11.2825624</v>
+        <v>11.196861225</v>
       </c>
       <c r="P34">
-        <v>33.8476872</v>
+        <v>33.590583675</v>
       </c>
       <c r="Q34">
-        <v>101.7476872</v>
+        <v>101.490583675</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1029965953103001</v>
+        <v>0.1036925305225441</v>
       </c>
       <c r="T34">
-        <v>1.114868102564615</v>
+        <v>1.128433175194781</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.114063488627781</v>
+        <v>4.959091867760272</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08316074545010456</v>
+        <v>0.08301180608920511</v>
       </c>
       <c r="C35">
-        <v>393.4726227117626</v>
+        <v>388.5508626105652</v>
       </c>
       <c r="D35">
-        <v>572.7396227117626</v>
+        <v>574.0168626105652</v>
       </c>
       <c r="E35">
-        <v>-233.333</v>
+        <v>-227.134</v>
       </c>
       <c r="F35">
-        <v>204.567</v>
+        <v>210.766</v>
       </c>
       <c r="G35">
         <v>25.3</v>
@@ -4151,28 +4151,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M35">
-        <v>11.3125551</v>
+        <v>11.6553598</v>
       </c>
       <c r="N35">
-        <v>44.7874449</v>
+        <v>44.44464019999999</v>
       </c>
       <c r="O35">
-        <v>11.196861225</v>
+        <v>11.11116005</v>
       </c>
       <c r="P35">
-        <v>33.590583675</v>
+        <v>33.33348015</v>
       </c>
       <c r="Q35">
-        <v>101.490583675</v>
+        <v>101.23348015</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1036925305225441</v>
+        <v>0.1044095546806138</v>
       </c>
       <c r="T35">
-        <v>1.128433175194781</v>
+        <v>1.142409310631923</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.959091867760272</v>
+        <v>4.813236224590852</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08301180608920511</v>
+        <v>0.08286286672830562</v>
       </c>
       <c r="C36">
-        <v>388.5508626105652</v>
+        <v>383.6348118677025</v>
       </c>
       <c r="D36">
-        <v>574.0168626105652</v>
+        <v>575.2998118677026</v>
       </c>
       <c r="E36">
-        <v>-227.134</v>
+        <v>-220.935</v>
       </c>
       <c r="F36">
-        <v>210.766</v>
+        <v>216.965</v>
       </c>
       <c r="G36">
         <v>25.3</v>
@@ -4233,28 +4233,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M36">
-        <v>11.6553598</v>
+        <v>11.9981645</v>
       </c>
       <c r="N36">
-        <v>44.44464019999999</v>
+        <v>44.10183549999999</v>
       </c>
       <c r="O36">
-        <v>11.11116005</v>
+        <v>11.025458875</v>
       </c>
       <c r="P36">
-        <v>33.33348015</v>
+        <v>33.07637662499999</v>
       </c>
       <c r="Q36">
-        <v>101.23348015</v>
+        <v>100.976376625</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1044095546806138</v>
+        <v>0.1051486411204702</v>
       </c>
       <c r="T36">
-        <v>1.142409310631923</v>
+        <v>1.156815481005591</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.813236224590852</v>
+        <v>4.675715189602542</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08286286672830562</v>
+        <v>0.08271392736740615</v>
       </c>
       <c r="C37">
-        <v>383.6348118677025</v>
+        <v>378.7245088508187</v>
       </c>
       <c r="D37">
-        <v>575.2998118677026</v>
+        <v>576.5885088508187</v>
       </c>
       <c r="E37">
-        <v>-220.935</v>
+        <v>-214.736</v>
       </c>
       <c r="F37">
-        <v>216.965</v>
+        <v>223.164</v>
       </c>
       <c r="G37">
         <v>25.3</v>
@@ -4315,28 +4315,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M37">
-        <v>11.9981645</v>
+        <v>12.3409692</v>
       </c>
       <c r="N37">
-        <v>44.10183549999999</v>
+        <v>43.75903079999999</v>
       </c>
       <c r="O37">
-        <v>11.025458875</v>
+        <v>10.9397577</v>
       </c>
       <c r="P37">
-        <v>33.07637662499999</v>
+        <v>32.81927309999999</v>
       </c>
       <c r="Q37">
-        <v>100.976376625</v>
+        <v>100.7192731</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1051486411204702</v>
+        <v>0.1059108240115721</v>
       </c>
       <c r="T37">
-        <v>1.156815481005591</v>
+        <v>1.171671844203437</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.675715189602542</v>
+        <v>4.545834212113582</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08271392736740617</v>
+        <v>0.0832587380065067</v>
       </c>
       <c r="C38">
-        <v>378.7245088508184</v>
+        <v>367.8393762348891</v>
       </c>
       <c r="D38">
-        <v>576.5885088508185</v>
+        <v>571.9023762348892</v>
       </c>
       <c r="E38">
-        <v>-214.736</v>
+        <v>-208.537</v>
       </c>
       <c r="F38">
-        <v>223.164</v>
+        <v>229.363</v>
       </c>
       <c r="G38">
         <v>25.3</v>
@@ -4397,45 +4397,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M38">
-        <v>12.3409692</v>
+        <v>13.2571814</v>
       </c>
       <c r="N38">
-        <v>43.75903079999999</v>
+        <v>42.84281859999999</v>
       </c>
       <c r="O38">
-        <v>10.9397577</v>
+        <v>10.71070465</v>
       </c>
       <c r="P38">
-        <v>32.81927309999999</v>
+        <v>32.13211395</v>
       </c>
       <c r="Q38">
-        <v>100.7192731</v>
+        <v>100.03211395</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1059108240115721</v>
+        <v>0.1066972031849313</v>
       </c>
       <c r="T38">
-        <v>1.171671844203437</v>
+        <v>1.186999837978992</v>
       </c>
       <c r="U38">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.25</v>
       </c>
       <c r="W38">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.545834212113583</v>
+        <v>4.231668731635519</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0832587380065067</v>
+        <v>0.08312854864560723</v>
       </c>
       <c r="C39">
-        <v>367.8393762348891</v>
+        <v>362.7532468751094</v>
       </c>
       <c r="D39">
-        <v>571.9023762348892</v>
+        <v>573.0152468751095</v>
       </c>
       <c r="E39">
-        <v>-208.537</v>
+        <v>-202.338</v>
       </c>
       <c r="F39">
-        <v>229.363</v>
+        <v>235.562</v>
       </c>
       <c r="G39">
         <v>25.3</v>
@@ -4479,28 +4479,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M39">
-        <v>13.2571814</v>
+        <v>13.6154836</v>
       </c>
       <c r="N39">
-        <v>42.84281859999999</v>
+        <v>42.4845164</v>
       </c>
       <c r="O39">
-        <v>10.71070465</v>
+        <v>10.6211291</v>
       </c>
       <c r="P39">
-        <v>32.13211395</v>
+        <v>31.8633873</v>
       </c>
       <c r="Q39">
-        <v>100.03211395</v>
+        <v>99.76338730000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1066972031849313</v>
+        <v>0.1075089494283988</v>
       </c>
       <c r="T39">
-        <v>1.186999837978992</v>
+        <v>1.202822283166662</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.231668731635519</v>
+        <v>4.120309028171427</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08312854864560723</v>
+        <v>0.08299835928470778</v>
       </c>
       <c r="C40">
-        <v>362.7532468751094</v>
+        <v>357.6714570522332</v>
       </c>
       <c r="D40">
-        <v>573.0152468751095</v>
+        <v>574.1324570522332</v>
       </c>
       <c r="E40">
-        <v>-202.338</v>
+        <v>-196.139</v>
       </c>
       <c r="F40">
-        <v>235.562</v>
+        <v>241.761</v>
       </c>
       <c r="G40">
         <v>25.3</v>
@@ -4561,28 +4561,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M40">
-        <v>13.6154836</v>
+        <v>13.9737858</v>
       </c>
       <c r="N40">
-        <v>42.4845164</v>
+        <v>42.12621419999999</v>
       </c>
       <c r="O40">
-        <v>10.6211291</v>
+        <v>10.53155355</v>
       </c>
       <c r="P40">
-        <v>31.8633873</v>
+        <v>31.59466064999999</v>
       </c>
       <c r="Q40">
-        <v>99.76338730000001</v>
+        <v>99.49466065</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1075089494283988</v>
+        <v>0.1083473103027996</v>
       </c>
       <c r="T40">
-        <v>1.202822283166662</v>
+        <v>1.21916349704901</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.120309028171427</v>
+        <v>4.014660078731133</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08299835928470778</v>
+        <v>0.08391816992380831</v>
       </c>
       <c r="C41">
-        <v>357.6714570522332</v>
+        <v>343.6712436087167</v>
       </c>
       <c r="D41">
-        <v>574.1324570522332</v>
+        <v>566.3312436087168</v>
       </c>
       <c r="E41">
-        <v>-196.139</v>
+        <v>-189.94</v>
       </c>
       <c r="F41">
-        <v>241.761</v>
+        <v>247.96</v>
       </c>
       <c r="G41">
         <v>25.3</v>
@@ -4643,45 +4643,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M41">
-        <v>13.9737858</v>
+        <v>15.199948</v>
       </c>
       <c r="N41">
-        <v>42.12621419999999</v>
+        <v>40.900052</v>
       </c>
       <c r="O41">
-        <v>10.53155355</v>
+        <v>10.225013</v>
       </c>
       <c r="P41">
-        <v>31.59466064999999</v>
+        <v>30.675039</v>
       </c>
       <c r="Q41">
-        <v>99.49466065</v>
+        <v>98.575039</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1083473103027996</v>
+        <v>0.1092136165396805</v>
       </c>
       <c r="T41">
-        <v>1.21916349704901</v>
+        <v>1.236049418060769</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.014660078731133</v>
+        <v>3.690802100112447</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08391816992380831</v>
+        <v>0.08381423056290883</v>
       </c>
       <c r="C42">
-        <v>343.6712436087167</v>
+        <v>338.3431461146323</v>
       </c>
       <c r="D42">
-        <v>566.3312436087168</v>
+        <v>567.2021461146323</v>
       </c>
       <c r="E42">
-        <v>-189.94</v>
+        <v>-183.741</v>
       </c>
       <c r="F42">
-        <v>247.96</v>
+        <v>254.159</v>
       </c>
       <c r="G42">
         <v>25.3</v>
@@ -4725,28 +4725,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M42">
-        <v>15.199948</v>
+        <v>15.5799467</v>
       </c>
       <c r="N42">
-        <v>40.900052</v>
+        <v>40.52005329999999</v>
       </c>
       <c r="O42">
-        <v>10.225013</v>
+        <v>10.130013325</v>
       </c>
       <c r="P42">
-        <v>30.675039</v>
+        <v>30.39003997499999</v>
       </c>
       <c r="Q42">
-        <v>98.575039</v>
+        <v>98.290039975</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1092136165396805</v>
+        <v>0.110109289089676</v>
       </c>
       <c r="T42">
-        <v>1.236049418060769</v>
+        <v>1.253507743174621</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.690802100112447</v>
+        <v>3.60078253669507</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08381423056290883</v>
+        <v>0.08371029120200936</v>
       </c>
       <c r="C43">
-        <v>338.3431461146323</v>
+        <v>333.0177312885252</v>
       </c>
       <c r="D43">
-        <v>567.2021461146323</v>
+        <v>568.0757312885253</v>
       </c>
       <c r="E43">
-        <v>-183.741</v>
+        <v>-177.542</v>
       </c>
       <c r="F43">
-        <v>254.159</v>
+        <v>260.358</v>
       </c>
       <c r="G43">
         <v>25.3</v>
@@ -4807,28 +4807,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M43">
-        <v>15.5799467</v>
+        <v>15.9599454</v>
       </c>
       <c r="N43">
-        <v>40.52005329999999</v>
+        <v>40.14005459999999</v>
       </c>
       <c r="O43">
-        <v>10.130013325</v>
+        <v>10.03501365</v>
       </c>
       <c r="P43">
-        <v>30.39003997499999</v>
+        <v>30.10504095</v>
       </c>
       <c r="Q43">
-        <v>98.290039975</v>
+        <v>98.00504094999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.110109289089676</v>
+        <v>0.1110358469000161</v>
       </c>
       <c r="T43">
-        <v>1.253507743174621</v>
+        <v>1.271568079499297</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.60078253669507</v>
+        <v>3.515049619154711</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08371029120200937</v>
+        <v>0.0845093518411099</v>
       </c>
       <c r="C44">
-        <v>333.0177312885251</v>
+        <v>320.1711861063893</v>
       </c>
       <c r="D44">
-        <v>568.0757312885252</v>
+        <v>561.4281861063893</v>
       </c>
       <c r="E44">
-        <v>-177.542</v>
+        <v>-171.343</v>
       </c>
       <c r="F44">
-        <v>260.358</v>
+        <v>266.557</v>
       </c>
       <c r="G44">
         <v>25.3</v>
@@ -4889,45 +4889,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M44">
-        <v>15.9599454</v>
+        <v>17.0863037</v>
       </c>
       <c r="N44">
-        <v>40.14005459999999</v>
+        <v>39.01369629999999</v>
       </c>
       <c r="O44">
-        <v>10.03501365</v>
+        <v>9.753424074999998</v>
       </c>
       <c r="P44">
-        <v>30.10504095</v>
+        <v>29.26027222499999</v>
       </c>
       <c r="Q44">
-        <v>98.00504094999999</v>
+        <v>97.160272225</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1110358469000161</v>
+        <v>0.1119949155107191</v>
       </c>
       <c r="T44">
-        <v>1.271568079499297</v>
+        <v>1.290262111835364</v>
       </c>
       <c r="U44">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.25</v>
       </c>
       <c r="W44">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.515049619154711</v>
+        <v>3.28333154935084</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0845093518411099</v>
+        <v>0.08442641248021045</v>
       </c>
       <c r="C45">
-        <v>320.1711861063893</v>
+        <v>314.6549303357916</v>
       </c>
       <c r="D45">
-        <v>561.4281861063893</v>
+        <v>562.1109303357916</v>
       </c>
       <c r="E45">
-        <v>-171.343</v>
+        <v>-165.144</v>
       </c>
       <c r="F45">
-        <v>266.557</v>
+        <v>272.756</v>
       </c>
       <c r="G45">
         <v>25.3</v>
@@ -4971,28 +4971,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M45">
-        <v>17.0863037</v>
+        <v>17.4836596</v>
       </c>
       <c r="N45">
-        <v>39.01369629999999</v>
+        <v>38.6163404</v>
       </c>
       <c r="O45">
-        <v>9.753424074999998</v>
+        <v>9.6540851</v>
       </c>
       <c r="P45">
-        <v>29.26027222499999</v>
+        <v>28.9622553</v>
       </c>
       <c r="Q45">
-        <v>97.160272225</v>
+        <v>96.8622553</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1119949155107191</v>
+        <v>0.1129882365718043</v>
       </c>
       <c r="T45">
-        <v>1.290262111835364</v>
+        <v>1.309623788183434</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.28333154935084</v>
+        <v>3.208710377774685</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08442641248021045</v>
+        <v>0.08434347311931097</v>
       </c>
       <c r="C46">
-        <v>314.6549303357916</v>
+        <v>309.1403371366497</v>
       </c>
       <c r="D46">
-        <v>562.1109303357916</v>
+        <v>562.7953371366498</v>
       </c>
       <c r="E46">
-        <v>-165.144</v>
+        <v>-158.945</v>
       </c>
       <c r="F46">
-        <v>272.756</v>
+        <v>278.955</v>
       </c>
       <c r="G46">
         <v>25.3</v>
@@ -5053,28 +5053,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M46">
-        <v>17.4836596</v>
+        <v>17.8810155</v>
       </c>
       <c r="N46">
-        <v>38.6163404</v>
+        <v>38.21898449999999</v>
       </c>
       <c r="O46">
-        <v>9.6540851</v>
+        <v>9.554746124999998</v>
       </c>
       <c r="P46">
-        <v>28.9622553</v>
+        <v>28.66423837499999</v>
       </c>
       <c r="Q46">
-        <v>96.8622553</v>
+        <v>96.564238375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1129882365718043</v>
+        <v>0.1140176783987472</v>
       </c>
       <c r="T46">
-        <v>1.309623788183434</v>
+        <v>1.329689525489615</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.208710377774685</v>
+        <v>3.137405702713025</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08434347311931097</v>
+        <v>0.08426053375841151</v>
       </c>
       <c r="C47">
-        <v>309.1403371366497</v>
+        <v>303.6274125892348</v>
       </c>
       <c r="D47">
-        <v>562.7953371366498</v>
+        <v>563.4814125892349</v>
       </c>
       <c r="E47">
-        <v>-158.945</v>
+        <v>-152.746</v>
       </c>
       <c r="F47">
-        <v>278.955</v>
+        <v>285.154</v>
       </c>
       <c r="G47">
         <v>25.3</v>
@@ -5135,28 +5135,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M47">
-        <v>17.8810155</v>
+        <v>18.2783714</v>
       </c>
       <c r="N47">
-        <v>38.21898449999999</v>
+        <v>37.8216286</v>
       </c>
       <c r="O47">
-        <v>9.554746124999998</v>
+        <v>9.455407149999999</v>
       </c>
       <c r="P47">
-        <v>28.66423837499999</v>
+        <v>28.36622145</v>
       </c>
       <c r="Q47">
-        <v>96.564238375</v>
+        <v>96.26622145</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1140176783987472</v>
+        <v>0.115085247700762</v>
       </c>
       <c r="T47">
-        <v>1.329689525489615</v>
+        <v>1.350498438251581</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.137405702713025</v>
+        <v>3.069201230914916</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08426053375841151</v>
+        <v>0.08417759439751202</v>
       </c>
       <c r="C48">
-        <v>303.6274125892348</v>
+        <v>298.1161628035035</v>
       </c>
       <c r="D48">
-        <v>563.4814125892349</v>
+        <v>564.1691628035036</v>
       </c>
       <c r="E48">
-        <v>-152.746</v>
+        <v>-146.547</v>
       </c>
       <c r="F48">
-        <v>285.154</v>
+        <v>291.353</v>
       </c>
       <c r="G48">
         <v>25.3</v>
@@ -5217,28 +5217,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M48">
-        <v>18.2783714</v>
+        <v>18.6757273</v>
       </c>
       <c r="N48">
-        <v>37.8216286</v>
+        <v>37.42427269999999</v>
       </c>
       <c r="O48">
-        <v>9.455407149999999</v>
+        <v>9.356068174999997</v>
       </c>
       <c r="P48">
-        <v>28.36622145</v>
+        <v>28.06820452499999</v>
       </c>
       <c r="Q48">
-        <v>96.26622145</v>
+        <v>95.968204525</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.115085247700762</v>
+        <v>0.1161931026368151</v>
       </c>
       <c r="T48">
-        <v>1.350498438251581</v>
+        <v>1.372092593004564</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.069201230914916</v>
+        <v>3.003899077065662</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08417759439751202</v>
+        <v>0.08690265503661256</v>
       </c>
       <c r="C49">
-        <v>298.1161628035035</v>
+        <v>270.165121672535</v>
       </c>
       <c r="D49">
-        <v>564.1691628035036</v>
+        <v>542.417121672535</v>
       </c>
       <c r="E49">
-        <v>-146.547</v>
+        <v>-140.348</v>
       </c>
       <c r="F49">
-        <v>291.353</v>
+        <v>297.552</v>
       </c>
       <c r="G49">
         <v>25.3</v>
@@ -5299,45 +5299,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M49">
-        <v>18.6757273</v>
+        <v>21.3939888</v>
       </c>
       <c r="N49">
-        <v>37.42427269999999</v>
+        <v>34.70601119999999</v>
       </c>
       <c r="O49">
-        <v>9.356068174999997</v>
+        <v>8.676502799999998</v>
       </c>
       <c r="P49">
-        <v>28.06820452499999</v>
+        <v>26.02950839999999</v>
       </c>
       <c r="Q49">
-        <v>95.968204525</v>
+        <v>93.9295084</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1161931026368151</v>
+        <v>0.1173435673781011</v>
       </c>
       <c r="T49">
-        <v>1.372092593004564</v>
+        <v>1.394517292171124</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.25</v>
       </c>
       <c r="W49">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.003899077065662</v>
+        <v>2.62223190469278</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08690265503661256</v>
+        <v>0.08687821567571309</v>
       </c>
       <c r="C50">
-        <v>270.165121672535</v>
+        <v>264.1537454749537</v>
       </c>
       <c r="D50">
-        <v>542.417121672535</v>
+        <v>542.6047454749537</v>
       </c>
       <c r="E50">
-        <v>-140.348</v>
+        <v>-134.149</v>
       </c>
       <c r="F50">
-        <v>297.552</v>
+        <v>303.751</v>
       </c>
       <c r="G50">
         <v>25.3</v>
@@ -5381,28 +5381,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M50">
-        <v>21.3939888</v>
+        <v>21.8396969</v>
       </c>
       <c r="N50">
-        <v>34.70601119999999</v>
+        <v>34.26030309999999</v>
       </c>
       <c r="O50">
-        <v>8.676502799999998</v>
+        <v>8.565075774999999</v>
       </c>
       <c r="P50">
-        <v>26.02950839999999</v>
+        <v>25.695227325</v>
       </c>
       <c r="Q50">
-        <v>93.9295084</v>
+        <v>93.595227325</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1173435673781011</v>
+        <v>0.1185391483837512</v>
       </c>
       <c r="T50">
-        <v>1.394517292171124</v>
+        <v>1.417821391304999</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.62223190469278</v>
+        <v>2.568716967862315</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08687821567571309</v>
+        <v>0.08685377631481363</v>
       </c>
       <c r="C51">
-        <v>264.1537454749537</v>
+        <v>258.1424991216223</v>
       </c>
       <c r="D51">
-        <v>542.6047454749537</v>
+        <v>542.7924991216223</v>
       </c>
       <c r="E51">
-        <v>-134.149</v>
+        <v>-127.95</v>
       </c>
       <c r="F51">
-        <v>303.751</v>
+        <v>309.95</v>
       </c>
       <c r="G51">
         <v>25.3</v>
@@ -5463,28 +5463,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M51">
-        <v>21.8396969</v>
+        <v>22.285405</v>
       </c>
       <c r="N51">
-        <v>34.26030309999999</v>
+        <v>33.814595</v>
       </c>
       <c r="O51">
-        <v>8.565075774999999</v>
+        <v>8.453648749999999</v>
       </c>
       <c r="P51">
-        <v>25.695227325</v>
+        <v>25.36094625</v>
       </c>
       <c r="Q51">
-        <v>93.595227325</v>
+        <v>93.26094625</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1185391483837512</v>
+        <v>0.1197825526296273</v>
       </c>
       <c r="T51">
-        <v>1.417821391304999</v>
+        <v>1.44205765440423</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.568716967862315</v>
+        <v>2.517342628505069</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08685377631481363</v>
+        <v>0.08832108695391415</v>
       </c>
       <c r="C52">
-        <v>258.1424991216223</v>
+        <v>240.8965867466117</v>
       </c>
       <c r="D52">
-        <v>542.7924991216223</v>
+        <v>531.7455867466117</v>
       </c>
       <c r="E52">
-        <v>-127.95</v>
+        <v>-121.751</v>
       </c>
       <c r="F52">
-        <v>309.95</v>
+        <v>316.149</v>
       </c>
       <c r="G52">
         <v>25.3</v>
@@ -5545,45 +5545,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M52">
-        <v>22.285405</v>
+        <v>23.9640942</v>
       </c>
       <c r="N52">
-        <v>33.814595</v>
+        <v>32.13590579999999</v>
       </c>
       <c r="O52">
-        <v>8.453648749999999</v>
+        <v>8.033976449999997</v>
       </c>
       <c r="P52">
-        <v>25.36094625</v>
+        <v>24.10192934999999</v>
       </c>
       <c r="Q52">
-        <v>93.26094625</v>
+        <v>92.00192935</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1197825526296273</v>
+        <v>0.1210767080692126</v>
       </c>
       <c r="T52">
-        <v>1.44205765440423</v>
+        <v>1.467283152732001</v>
       </c>
       <c r="U52">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.517342628505069</v>
+        <v>2.34100231503847</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08832108695391415</v>
+        <v>0.08832589759301468</v>
       </c>
       <c r="C53">
-        <v>240.8965867466117</v>
+        <v>234.6621084550133</v>
       </c>
       <c r="D53">
-        <v>531.7455867466117</v>
+        <v>531.7101084550134</v>
       </c>
       <c r="E53">
-        <v>-121.751</v>
+        <v>-115.552</v>
       </c>
       <c r="F53">
-        <v>316.149</v>
+        <v>322.348</v>
       </c>
       <c r="G53">
         <v>25.3</v>
@@ -5627,28 +5627,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M53">
-        <v>23.9640942</v>
+        <v>24.4339784</v>
       </c>
       <c r="N53">
-        <v>32.13590579999999</v>
+        <v>31.66602159999999</v>
       </c>
       <c r="O53">
-        <v>8.033976449999997</v>
+        <v>7.916505399999997</v>
       </c>
       <c r="P53">
-        <v>24.10192934999999</v>
+        <v>23.74951619999999</v>
       </c>
       <c r="Q53">
-        <v>92.00192935</v>
+        <v>91.64951619999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1210767080692126</v>
+        <v>0.1224247866521139</v>
       </c>
       <c r="T53">
-        <v>1.467283152732001</v>
+        <v>1.493559713490095</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.34100231503847</v>
+        <v>2.295983039749269</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08832589759301468</v>
+        <v>0.08833070823211522</v>
       </c>
       <c r="C54">
-        <v>234.6621084550133</v>
+        <v>228.4276348973525</v>
       </c>
       <c r="D54">
-        <v>531.7101084550134</v>
+        <v>531.6746348973526</v>
       </c>
       <c r="E54">
-        <v>-115.552</v>
+        <v>-109.353</v>
       </c>
       <c r="F54">
-        <v>322.348</v>
+        <v>328.547</v>
       </c>
       <c r="G54">
         <v>25.3</v>
@@ -5709,28 +5709,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M54">
-        <v>24.4339784</v>
+        <v>24.9038626</v>
       </c>
       <c r="N54">
-        <v>31.66602159999999</v>
+        <v>31.19613739999999</v>
       </c>
       <c r="O54">
-        <v>7.916505399999997</v>
+        <v>7.799034349999998</v>
       </c>
       <c r="P54">
-        <v>23.74951619999999</v>
+        <v>23.39710304999999</v>
       </c>
       <c r="Q54">
-        <v>91.64951619999999</v>
+        <v>91.29710305</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1224247866521139</v>
+        <v>0.1238302302810962</v>
       </c>
       <c r="T54">
-        <v>1.493559713490095</v>
+        <v>1.520954425769811</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.295983039749269</v>
+        <v>2.252662605037019</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08833070823211522</v>
+        <v>0.08833551887121575</v>
       </c>
       <c r="C55">
-        <v>228.4276348973525</v>
+        <v>222.1931660726819</v>
       </c>
       <c r="D55">
-        <v>531.6746348973526</v>
+        <v>531.639166072682</v>
       </c>
       <c r="E55">
-        <v>-109.353</v>
+        <v>-103.1539999999999</v>
       </c>
       <c r="F55">
-        <v>328.547</v>
+        <v>334.746</v>
       </c>
       <c r="G55">
         <v>25.3</v>
@@ -5791,28 +5791,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M55">
-        <v>24.9038626</v>
+        <v>25.37374680000001</v>
       </c>
       <c r="N55">
-        <v>31.19613739999999</v>
+        <v>30.72625319999999</v>
       </c>
       <c r="O55">
-        <v>7.799034349999998</v>
+        <v>7.681563299999997</v>
       </c>
       <c r="P55">
-        <v>23.39710304999999</v>
+        <v>23.04468989999999</v>
       </c>
       <c r="Q55">
-        <v>91.29710305</v>
+        <v>90.9446899</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1238302302810962</v>
+        <v>0.1252967801548169</v>
       </c>
       <c r="T55">
-        <v>1.520954425769811</v>
+        <v>1.549540212496471</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.252662605037019</v>
+        <v>2.210946630869667</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08833551887121575</v>
+        <v>0.08834032951031628</v>
       </c>
       <c r="C56">
-        <v>222.1931660726819</v>
+        <v>215.9587019800542</v>
       </c>
       <c r="D56">
-        <v>531.639166072682</v>
+        <v>531.6037019800542</v>
       </c>
       <c r="E56">
-        <v>-103.1539999999999</v>
+        <v>-96.95499999999998</v>
       </c>
       <c r="F56">
-        <v>334.746</v>
+        <v>340.945</v>
       </c>
       <c r="G56">
         <v>25.3</v>
@@ -5873,28 +5873,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M56">
-        <v>25.37374680000001</v>
+        <v>25.843631</v>
       </c>
       <c r="N56">
-        <v>30.72625319999999</v>
+        <v>30.25636899999999</v>
       </c>
       <c r="O56">
-        <v>7.681563299999997</v>
+        <v>7.564092249999998</v>
       </c>
       <c r="P56">
-        <v>23.04468989999999</v>
+        <v>22.69227674999999</v>
       </c>
       <c r="Q56">
-        <v>90.9446899</v>
+        <v>90.59227675</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1252967801548169</v>
+        <v>0.1268285100229251</v>
       </c>
       <c r="T56">
-        <v>1.549540212496471</v>
+        <v>1.579396478633205</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.210946630869667</v>
+        <v>2.170747601217491</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08834032951031628</v>
+        <v>0.0883451401494168</v>
       </c>
       <c r="C57">
-        <v>215.9587019800542</v>
+        <v>209.7242426185226</v>
       </c>
       <c r="D57">
-        <v>531.6037019800542</v>
+        <v>531.5682426185226</v>
       </c>
       <c r="E57">
-        <v>-96.95499999999998</v>
+        <v>-90.75599999999997</v>
       </c>
       <c r="F57">
-        <v>340.945</v>
+        <v>347.144</v>
       </c>
       <c r="G57">
         <v>25.3</v>
@@ -5955,28 +5955,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M57">
-        <v>25.843631</v>
+        <v>26.3135152</v>
       </c>
       <c r="N57">
-        <v>30.25636899999999</v>
+        <v>29.78648479999999</v>
       </c>
       <c r="O57">
-        <v>7.564092249999998</v>
+        <v>7.446621199999998</v>
       </c>
       <c r="P57">
-        <v>22.69227674999999</v>
+        <v>22.33986359999999</v>
       </c>
       <c r="Q57">
-        <v>90.59227675</v>
+        <v>90.23986360000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1268285100229251</v>
+        <v>0.1284298639759473</v>
       </c>
       <c r="T57">
-        <v>1.579396478633205</v>
+        <v>1.610609847776153</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.170747601217491</v>
+        <v>2.131984251195751</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0883451401494168</v>
+        <v>0.08834995078851735</v>
       </c>
       <c r="C58">
-        <v>209.7242426185226</v>
+        <v>203.4897879871402</v>
       </c>
       <c r="D58">
-        <v>531.5682426185226</v>
+        <v>531.5327879871403</v>
       </c>
       <c r="E58">
-        <v>-90.75599999999997</v>
+        <v>-84.55699999999996</v>
       </c>
       <c r="F58">
-        <v>347.144</v>
+        <v>353.343</v>
       </c>
       <c r="G58">
         <v>25.3</v>
@@ -6037,28 +6037,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M58">
-        <v>26.3135152</v>
+        <v>26.7833994</v>
       </c>
       <c r="N58">
-        <v>29.78648479999999</v>
+        <v>29.31660059999999</v>
       </c>
       <c r="O58">
-        <v>7.446621199999998</v>
+        <v>7.329150149999998</v>
       </c>
       <c r="P58">
-        <v>22.33986359999999</v>
+        <v>21.98745044999999</v>
       </c>
       <c r="Q58">
-        <v>90.23986360000001</v>
+        <v>89.88745045</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1284298639759473</v>
+        <v>0.1301056995081799</v>
       </c>
       <c r="T58">
-        <v>1.610609847776153</v>
+        <v>1.643275001530402</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.131984251195751</v>
+        <v>2.094581018718632</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08834995078851735</v>
+        <v>0.08835476142761789</v>
       </c>
       <c r="C59">
-        <v>203.4897879871402</v>
+        <v>197.2553380849608</v>
       </c>
       <c r="D59">
-        <v>531.5327879871403</v>
+        <v>531.4973380849609</v>
       </c>
       <c r="E59">
-        <v>-84.55699999999996</v>
+        <v>-78.35799999999995</v>
       </c>
       <c r="F59">
-        <v>353.343</v>
+        <v>359.542</v>
       </c>
       <c r="G59">
         <v>25.3</v>
@@ -6119,28 +6119,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M59">
-        <v>26.7833994</v>
+        <v>27.2532836</v>
       </c>
       <c r="N59">
-        <v>29.31660059999999</v>
+        <v>28.84671639999999</v>
       </c>
       <c r="O59">
-        <v>7.329150149999998</v>
+        <v>7.211679099999998</v>
       </c>
       <c r="P59">
-        <v>21.98745044999999</v>
+        <v>21.63503729999999</v>
       </c>
       <c r="Q59">
-        <v>89.88745045</v>
+        <v>89.5350373</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1301056995081799</v>
+        <v>0.1318613367324235</v>
       </c>
       <c r="T59">
-        <v>1.643275001530402</v>
+        <v>1.677495638796758</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.094581018718632</v>
+        <v>2.058467552878655</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08835476142761789</v>
+        <v>0.08835957206671842</v>
       </c>
       <c r="C60">
-        <v>197.2553380849609</v>
+        <v>191.0208929110383</v>
       </c>
       <c r="D60">
-        <v>531.4973380849609</v>
+        <v>531.4618929110384</v>
       </c>
       <c r="E60">
-        <v>-78.358</v>
+        <v>-72.15899999999999</v>
       </c>
       <c r="F60">
-        <v>359.542</v>
+        <v>365.741</v>
       </c>
       <c r="G60">
         <v>25.3</v>
@@ -6201,28 +6201,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M60">
-        <v>27.2532836</v>
+        <v>27.7231678</v>
       </c>
       <c r="N60">
-        <v>28.84671639999999</v>
+        <v>28.37683219999999</v>
       </c>
       <c r="O60">
-        <v>7.211679099999999</v>
+        <v>7.094208049999998</v>
       </c>
       <c r="P60">
-        <v>21.6350373</v>
+        <v>21.28262414999999</v>
       </c>
       <c r="Q60">
-        <v>89.5350373</v>
+        <v>89.18262415</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1318613367324235</v>
+        <v>0.1337026147968742</v>
       </c>
       <c r="T60">
-        <v>1.677495638796757</v>
+        <v>1.71338557544196</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.058467552878656</v>
+        <v>2.02357827232139</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08835957206671842</v>
+        <v>0.09475438270581896</v>
       </c>
       <c r="C61">
-        <v>191.0208929110383</v>
+        <v>141.5441498028186</v>
       </c>
       <c r="D61">
-        <v>531.4618929110384</v>
+        <v>488.1841498028186</v>
       </c>
       <c r="E61">
-        <v>-72.15899999999999</v>
+        <v>-65.95999999999998</v>
       </c>
       <c r="F61">
-        <v>365.741</v>
+        <v>371.94</v>
       </c>
       <c r="G61">
         <v>25.3</v>
@@ -6283,45 +6283,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M61">
-        <v>27.7231678</v>
+        <v>33.4746</v>
       </c>
       <c r="N61">
-        <v>28.37683219999999</v>
+        <v>22.6254</v>
       </c>
       <c r="O61">
-        <v>7.094208049999998</v>
+        <v>5.65635</v>
       </c>
       <c r="P61">
-        <v>21.28262414999999</v>
+        <v>16.96905</v>
       </c>
       <c r="Q61">
-        <v>89.18262415</v>
+        <v>84.86905</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1337026147968742</v>
+        <v>0.1356359567645474</v>
       </c>
       <c r="T61">
-        <v>1.71338557544196</v>
+        <v>1.751070008919422</v>
       </c>
       <c r="U61">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V61">
         <v>0.25</v>
       </c>
       <c r="W61">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.02357827232139</v>
+        <v>1.675897546199208</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09475438270581896</v>
+        <v>0.09486569334491948</v>
       </c>
       <c r="C62">
-        <v>141.5441498028186</v>
+        <v>134.6541626211666</v>
       </c>
       <c r="D62">
-        <v>488.1841498028186</v>
+        <v>487.4931626211665</v>
       </c>
       <c r="E62">
-        <v>-65.95999999999998</v>
+        <v>-59.76100000000002</v>
       </c>
       <c r="F62">
-        <v>371.94</v>
+        <v>378.139</v>
       </c>
       <c r="G62">
         <v>25.3</v>
@@ -6365,28 +6365,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M62">
-        <v>33.4746</v>
+        <v>34.03250999999999</v>
       </c>
       <c r="N62">
-        <v>22.6254</v>
+        <v>22.06749</v>
       </c>
       <c r="O62">
-        <v>5.65635</v>
+        <v>5.5168725</v>
       </c>
       <c r="P62">
-        <v>16.96905</v>
+        <v>16.5506175</v>
       </c>
       <c r="Q62">
-        <v>84.86905</v>
+        <v>84.45061750000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1356359567645474</v>
+        <v>0.1376684444741525</v>
       </c>
       <c r="T62">
-        <v>1.751070008919422</v>
+        <v>1.790686977447011</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.675897546199208</v>
+        <v>1.648423815933647</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09486569334491948</v>
+        <v>0.09497700398402002</v>
       </c>
       <c r="C63">
-        <v>134.6541626211666</v>
+        <v>127.7661287533529</v>
       </c>
       <c r="D63">
-        <v>487.4931626211665</v>
+        <v>486.8041287533529</v>
       </c>
       <c r="E63">
-        <v>-59.76100000000002</v>
+        <v>-53.56200000000001</v>
       </c>
       <c r="F63">
-        <v>378.139</v>
+        <v>384.338</v>
       </c>
       <c r="G63">
         <v>25.3</v>
@@ -6447,28 +6447,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M63">
-        <v>34.03250999999999</v>
+        <v>34.59041999999999</v>
       </c>
       <c r="N63">
-        <v>22.06749</v>
+        <v>21.50958</v>
       </c>
       <c r="O63">
-        <v>5.5168725</v>
+        <v>5.377395</v>
       </c>
       <c r="P63">
-        <v>16.5506175</v>
+        <v>16.132185</v>
       </c>
       <c r="Q63">
-        <v>84.45061750000001</v>
+        <v>84.032185</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1376684444741525</v>
+        <v>0.1398079052211053</v>
       </c>
       <c r="T63">
-        <v>1.790686977447011</v>
+        <v>1.832389049581315</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.648423815933647</v>
+        <v>1.621836335031491</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09497700398402002</v>
+        <v>0.09508831462312055</v>
       </c>
       <c r="C64">
-        <v>127.7661287533529</v>
+        <v>120.8800399284944</v>
       </c>
       <c r="D64">
-        <v>486.8041287533529</v>
+        <v>486.1170399284944</v>
       </c>
       <c r="E64">
-        <v>-53.56200000000001</v>
+        <v>-47.363</v>
       </c>
       <c r="F64">
-        <v>384.338</v>
+        <v>390.537</v>
       </c>
       <c r="G64">
         <v>25.3</v>
@@ -6529,28 +6529,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M64">
-        <v>34.59041999999999</v>
+        <v>35.14832999999999</v>
       </c>
       <c r="N64">
-        <v>21.50958</v>
+        <v>20.95167</v>
       </c>
       <c r="O64">
-        <v>5.377395</v>
+        <v>5.2379175</v>
       </c>
       <c r="P64">
-        <v>16.132185</v>
+        <v>15.7137525</v>
       </c>
       <c r="Q64">
-        <v>84.032185</v>
+        <v>83.6137525</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1398079052211053</v>
+        <v>0.1420630124949204</v>
       </c>
       <c r="T64">
-        <v>1.832389049581315</v>
+        <v>1.876345287776933</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.621836335031491</v>
+        <v>1.596092901142103</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09508831462312055</v>
+        <v>0.09519962526222109</v>
       </c>
       <c r="C65">
-        <v>120.8800399284944</v>
+        <v>113.9958879223361</v>
       </c>
       <c r="D65">
-        <v>486.1170399284944</v>
+        <v>485.4318879223361</v>
       </c>
       <c r="E65">
-        <v>-47.363</v>
+        <v>-41.16399999999999</v>
       </c>
       <c r="F65">
-        <v>390.537</v>
+        <v>396.736</v>
       </c>
       <c r="G65">
         <v>25.3</v>
@@ -6611,28 +6611,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M65">
-        <v>35.14832999999999</v>
+        <v>35.70624</v>
       </c>
       <c r="N65">
-        <v>20.95167</v>
+        <v>20.39375999999999</v>
       </c>
       <c r="O65">
-        <v>5.2379175</v>
+        <v>5.098439999999998</v>
       </c>
       <c r="P65">
-        <v>15.7137525</v>
+        <v>15.29531999999999</v>
       </c>
       <c r="Q65">
-        <v>83.6137525</v>
+        <v>83.19532</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1420630124949204</v>
+        <v>0.1444434035061697</v>
       </c>
       <c r="T65">
-        <v>1.876345287776933</v>
+        <v>1.92274353920564</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.596092901142103</v>
+        <v>1.571153949561757</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09519962526222109</v>
+        <v>0.09531093590132161</v>
       </c>
       <c r="C66">
-        <v>113.9958879223361</v>
+        <v>107.1136645569249</v>
       </c>
       <c r="D66">
-        <v>485.4318879223361</v>
+        <v>484.7486645569249</v>
       </c>
       <c r="E66">
-        <v>-41.16399999999999</v>
+        <v>-34.96499999999997</v>
       </c>
       <c r="F66">
-        <v>396.736</v>
+        <v>402.935</v>
       </c>
       <c r="G66">
         <v>25.3</v>
@@ -6693,28 +6693,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M66">
-        <v>35.70624</v>
+        <v>36.26415</v>
       </c>
       <c r="N66">
-        <v>20.39375999999999</v>
+        <v>19.83584999999999</v>
       </c>
       <c r="O66">
-        <v>5.098439999999998</v>
+        <v>4.958962499999998</v>
       </c>
       <c r="P66">
-        <v>15.29531999999999</v>
+        <v>14.8768875</v>
       </c>
       <c r="Q66">
-        <v>83.19532</v>
+        <v>82.7768875</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1444434035061697</v>
+        <v>0.1469598168609189</v>
       </c>
       <c r="T66">
-        <v>1.92274353920564</v>
+        <v>1.971793119287417</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.571153949561757</v>
+        <v>1.54698235033773</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09531093590132161</v>
+        <v>0.09542224654042214</v>
       </c>
       <c r="C67">
-        <v>107.1136645569249</v>
+        <v>100.2333617002829</v>
       </c>
       <c r="D67">
-        <v>484.7486645569249</v>
+        <v>484.0673617002829</v>
       </c>
       <c r="E67">
-        <v>-34.96499999999997</v>
+        <v>-28.76599999999996</v>
       </c>
       <c r="F67">
-        <v>402.935</v>
+        <v>409.134</v>
       </c>
       <c r="G67">
         <v>25.3</v>
@@ -6775,28 +6775,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M67">
-        <v>36.26415</v>
+        <v>36.82206</v>
       </c>
       <c r="N67">
-        <v>19.83584999999999</v>
+        <v>19.27793999999999</v>
       </c>
       <c r="O67">
-        <v>4.958962499999998</v>
+        <v>4.819484999999998</v>
       </c>
       <c r="P67">
-        <v>14.8768875</v>
+        <v>14.458455</v>
       </c>
       <c r="Q67">
-        <v>82.7768875</v>
+        <v>82.35845500000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1469598168609189</v>
+        <v>0.1496242545306534</v>
       </c>
       <c r="T67">
-        <v>1.971793119287417</v>
+        <v>2.023727968785769</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.54698235033773</v>
+        <v>1.523543223817462</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09542224654042214</v>
+        <v>0.09553355717952269</v>
       </c>
       <c r="C68">
-        <v>100.2333617002829</v>
+        <v>93.35497126608533</v>
       </c>
       <c r="D68">
-        <v>484.0673617002829</v>
+        <v>483.3879712660853</v>
       </c>
       <c r="E68">
-        <v>-28.76599999999996</v>
+        <v>-22.56699999999995</v>
       </c>
       <c r="F68">
-        <v>409.134</v>
+        <v>415.333</v>
       </c>
       <c r="G68">
         <v>25.3</v>
@@ -6857,28 +6857,28 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M68">
-        <v>36.82206</v>
+        <v>37.37997</v>
       </c>
       <c r="N68">
-        <v>19.27793999999999</v>
+        <v>18.72002999999999</v>
       </c>
       <c r="O68">
-        <v>4.819484999999998</v>
+        <v>4.680007499999999</v>
       </c>
       <c r="P68">
-        <v>14.458455</v>
+        <v>14.0400225</v>
       </c>
       <c r="Q68">
-        <v>82.35845500000001</v>
+        <v>81.9400225</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1496242545306534</v>
+        <v>0.1524501732712809</v>
       </c>
       <c r="T68">
-        <v>2.023727968785769</v>
+        <v>2.078810384920384</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.523543223817462</v>
+        <v>1.500803772715708</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09553355717952269</v>
+        <v>0.1276156471101426</v>
       </c>
       <c r="C69">
-        <v>93.35497126608533</v>
+        <v>-52.0659515372534</v>
       </c>
       <c r="D69">
-        <v>483.3879712660853</v>
+        <v>344.1660484627466</v>
       </c>
       <c r="E69">
-        <v>-22.56699999999995</v>
+        <v>-16.36799999999994</v>
       </c>
       <c r="F69">
-        <v>415.333</v>
+        <v>421.532</v>
       </c>
       <c r="G69">
         <v>25.3</v>
@@ -6939,45 +6939,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M69">
-        <v>37.37997</v>
+        <v>61.88089760000001</v>
       </c>
       <c r="N69">
-        <v>18.72002999999999</v>
+        <v>-5.780897600000017</v>
       </c>
       <c r="O69">
-        <v>4.680007499999999</v>
+        <v>-1.445224400000004</v>
       </c>
       <c r="P69">
-        <v>14.0400225</v>
+        <v>-4.335673200000013</v>
       </c>
       <c r="Q69">
-        <v>81.9400225</v>
+        <v>63.56432679999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1524501732712809</v>
+        <v>0.1575508249494746</v>
       </c>
       <c r="T69">
-        <v>2.078810384920384</v>
+        <v>2.178231579966357</v>
       </c>
       <c r="U69">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.25</v>
+        <v>0.2266450640496203</v>
       </c>
       <c r="W69">
-        <v>0.0675</v>
+        <v>0.1135285045975158</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.500803772715708</v>
+        <v>0.9065802561984813</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1276156471101426</v>
+        <v>0.1286256471101426</v>
       </c>
       <c r="C70">
-        <v>-52.0659515372534</v>
+        <v>-61.35751393065345</v>
       </c>
       <c r="D70">
-        <v>344.1660484627466</v>
+        <v>341.0734860693465</v>
       </c>
       <c r="E70">
-        <v>-16.36799999999994</v>
+        <v>-10.16899999999998</v>
       </c>
       <c r="F70">
-        <v>421.532</v>
+        <v>427.731</v>
       </c>
       <c r="G70">
         <v>25.3</v>
@@ -7021,37 +7021,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M70">
-        <v>61.88089760000001</v>
+        <v>62.79091080000001</v>
       </c>
       <c r="N70">
-        <v>-5.780897600000017</v>
+        <v>-6.690910800000012</v>
       </c>
       <c r="O70">
-        <v>-1.445224400000004</v>
+        <v>-1.672727700000003</v>
       </c>
       <c r="P70">
-        <v>-4.335673200000013</v>
+        <v>-5.018183100000009</v>
       </c>
       <c r="Q70">
-        <v>63.56432679999999</v>
+        <v>62.8818169</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1575508249494746</v>
+        <v>0.1611556902704254</v>
       </c>
       <c r="T70">
-        <v>2.178231579966357</v>
+        <v>2.248497114803981</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2266450640496203</v>
+        <v>0.2233603529764374</v>
       </c>
       <c r="W70">
-        <v>0.1135285045975158</v>
+        <v>0.114010700183059</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9065802561984813</v>
+        <v>0.8934414119057498</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1286256471101426</v>
+        <v>0.1296356471101426</v>
       </c>
       <c r="C71">
-        <v>-61.35751393065345</v>
+        <v>-70.59399378983807</v>
       </c>
       <c r="D71">
-        <v>341.0734860693465</v>
+        <v>338.0360062101619</v>
       </c>
       <c r="E71">
-        <v>-10.16899999999998</v>
+        <v>-3.96999999999997</v>
       </c>
       <c r="F71">
-        <v>427.731</v>
+        <v>433.93</v>
       </c>
       <c r="G71">
         <v>25.3</v>
@@ -7103,37 +7103,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M71">
-        <v>62.79091080000001</v>
+        <v>63.70092400000001</v>
       </c>
       <c r="N71">
-        <v>-6.690910800000012</v>
+        <v>-7.600924000000013</v>
       </c>
       <c r="O71">
-        <v>-1.672727700000003</v>
+        <v>-1.900231000000003</v>
       </c>
       <c r="P71">
-        <v>-5.018183100000009</v>
+        <v>-5.70069300000001</v>
       </c>
       <c r="Q71">
-        <v>62.8818169</v>
+        <v>62.199307</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1611556902704254</v>
+        <v>0.1650008799461063</v>
       </c>
       <c r="T71">
-        <v>2.248497114803981</v>
+        <v>2.32344701863078</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2233603529764374</v>
+        <v>0.2201694907910597</v>
       </c>
       <c r="W71">
-        <v>0.114010700183059</v>
+        <v>0.1144791187518724</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8934414119057498</v>
+        <v>0.880677963164239</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1296356471101426</v>
+        <v>0.1306456471101426</v>
       </c>
       <c r="C72">
-        <v>-70.59399378983807</v>
+        <v>-79.77684976133247</v>
       </c>
       <c r="D72">
-        <v>338.0360062101619</v>
+        <v>335.0521502386675</v>
       </c>
       <c r="E72">
-        <v>-3.96999999999997</v>
+        <v>2.229000000000042</v>
       </c>
       <c r="F72">
-        <v>433.93</v>
+        <v>440.129</v>
       </c>
       <c r="G72">
         <v>25.3</v>
@@ -7185,37 +7185,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M72">
-        <v>63.70092400000001</v>
+        <v>64.61093720000001</v>
       </c>
       <c r="N72">
-        <v>-7.600924000000013</v>
+        <v>-8.510937200000015</v>
       </c>
       <c r="O72">
-        <v>-1.900231000000003</v>
+        <v>-2.127734300000004</v>
       </c>
       <c r="P72">
-        <v>-5.70069300000001</v>
+        <v>-6.383202900000011</v>
       </c>
       <c r="Q72">
-        <v>62.199307</v>
+        <v>61.51679709999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1650008799461063</v>
+        <v>0.1691112551166617</v>
       </c>
       <c r="T72">
-        <v>2.32344701863078</v>
+        <v>2.403565881342187</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2201694907910597</v>
+        <v>0.2170685120475237</v>
       </c>
       <c r="W72">
-        <v>0.1144791187518724</v>
+        <v>0.1149343424314235</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.880677963164239</v>
+        <v>0.8682740481900948</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1306456471101426</v>
+        <v>0.1316556471101426</v>
       </c>
       <c r="C73">
-        <v>-79.77684976133241</v>
+        <v>-88.90748944019407</v>
       </c>
       <c r="D73">
-        <v>335.0521502386675</v>
+        <v>332.1205105598059</v>
       </c>
       <c r="E73">
-        <v>2.228999999999985</v>
+        <v>8.427999999999997</v>
       </c>
       <c r="F73">
-        <v>440.129</v>
+        <v>446.328</v>
       </c>
       <c r="G73">
         <v>25.3</v>
@@ -7267,37 +7267,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M73">
-        <v>64.6109372</v>
+        <v>65.5209504</v>
       </c>
       <c r="N73">
-        <v>-8.510937200000001</v>
+        <v>-9.420950400000009</v>
       </c>
       <c r="O73">
-        <v>-2.1277343</v>
+        <v>-2.355237600000002</v>
       </c>
       <c r="P73">
-        <v>-6.383202900000001</v>
+        <v>-7.065712800000007</v>
       </c>
       <c r="Q73">
-        <v>61.51679710000001</v>
+        <v>60.8342872</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1691112551166616</v>
+        <v>0.1735152285136853</v>
       </c>
       <c r="T73">
-        <v>2.403565881342186</v>
+        <v>2.48940751996155</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2170685120475237</v>
+        <v>0.2140536716024192</v>
       </c>
       <c r="W73">
-        <v>0.1149343424314235</v>
+        <v>0.1153769210087649</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.868274048190095</v>
+        <v>0.8562146864096769</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1316556471101426</v>
+        <v>0.1326656471101426</v>
       </c>
       <c r="C74">
-        <v>-88.90748944019407</v>
+        <v>-97.98727158409076</v>
       </c>
       <c r="D74">
-        <v>332.1205105598059</v>
+        <v>329.2397284159092</v>
       </c>
       <c r="E74">
-        <v>8.427999999999997</v>
+        <v>14.62700000000001</v>
       </c>
       <c r="F74">
-        <v>446.328</v>
+        <v>452.527</v>
       </c>
       <c r="G74">
         <v>25.3</v>
@@ -7349,37 +7349,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M74">
-        <v>65.5209504</v>
+        <v>66.4309636</v>
       </c>
       <c r="N74">
-        <v>-9.420950400000009</v>
+        <v>-10.3309636</v>
       </c>
       <c r="O74">
-        <v>-2.355237600000002</v>
+        <v>-2.582740900000001</v>
       </c>
       <c r="P74">
-        <v>-7.065712800000007</v>
+        <v>-7.748222700000003</v>
       </c>
       <c r="Q74">
-        <v>60.8342872</v>
+        <v>60.15177730000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1735152285136853</v>
+        <v>0.1782454221623403</v>
       </c>
       <c r="T74">
-        <v>2.48940751996155</v>
+        <v>2.581607798478644</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2140536716024192</v>
+        <v>0.2111214295256738</v>
       </c>
       <c r="W74">
-        <v>0.1153769210087649</v>
+        <v>0.1158073741456311</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8562146864096769</v>
+        <v>0.844485718102695</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1326656471101426</v>
+        <v>0.1336756471101426</v>
       </c>
       <c r="C75">
-        <v>-97.98727158409076</v>
+        <v>-107.0175082131411</v>
       </c>
       <c r="D75">
-        <v>329.2397284159092</v>
+        <v>326.4084917868589</v>
       </c>
       <c r="E75">
-        <v>14.62700000000001</v>
+        <v>20.82600000000002</v>
       </c>
       <c r="F75">
-        <v>452.527</v>
+        <v>458.726</v>
       </c>
       <c r="G75">
         <v>25.3</v>
@@ -7431,37 +7431,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M75">
-        <v>66.4309636</v>
+        <v>67.34097680000001</v>
       </c>
       <c r="N75">
-        <v>-10.3309636</v>
+        <v>-11.24097680000001</v>
       </c>
       <c r="O75">
-        <v>-2.582740900000001</v>
+        <v>-2.810244200000003</v>
       </c>
       <c r="P75">
-        <v>-7.748222700000003</v>
+        <v>-8.43073260000001</v>
       </c>
       <c r="Q75">
-        <v>60.15177730000001</v>
+        <v>59.46926739999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1782454221623403</v>
+        <v>0.1833394768608918</v>
       </c>
       <c r="T75">
-        <v>2.581607798478644</v>
+        <v>2.680900406112438</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2111214295256738</v>
+        <v>0.2082684372347862</v>
       </c>
       <c r="W75">
-        <v>0.1158073741456311</v>
+        <v>0.1162261934139334</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.844485718102695</v>
+        <v>0.833073748939145</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1336756471101426</v>
+        <v>0.1346856471101426</v>
       </c>
       <c r="C76">
-        <v>-107.0175082131411</v>
+        <v>-115.9994666023363</v>
       </c>
       <c r="D76">
-        <v>326.4084917868589</v>
+        <v>323.6255333976637</v>
       </c>
       <c r="E76">
-        <v>20.82600000000002</v>
+        <v>27.02499999999998</v>
       </c>
       <c r="F76">
-        <v>458.726</v>
+        <v>464.925</v>
       </c>
       <c r="G76">
         <v>25.3</v>
@@ -7513,37 +7513,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M76">
-        <v>67.34097680000001</v>
+        <v>68.25099</v>
       </c>
       <c r="N76">
-        <v>-11.24097680000001</v>
+        <v>-12.15099000000001</v>
       </c>
       <c r="O76">
-        <v>-2.810244200000003</v>
+        <v>-3.037747500000002</v>
       </c>
       <c r="P76">
-        <v>-8.43073260000001</v>
+        <v>-9.113242500000005</v>
       </c>
       <c r="Q76">
-        <v>59.46926739999999</v>
+        <v>58.7867575</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1833394768608918</v>
+        <v>0.1888410559353275</v>
       </c>
       <c r="T76">
-        <v>2.680900406112438</v>
+        <v>2.788136422356936</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2082684372347862</v>
+        <v>0.2054915247383224</v>
       </c>
       <c r="W76">
-        <v>0.1162261934139334</v>
+        <v>0.1166338441684143</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.833073748939145</v>
+        <v>0.8219660989532898</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1346856471101426</v>
+        <v>0.1356956471101426</v>
       </c>
       <c r="C77">
-        <v>-115.9994666023363</v>
+        <v>-124.934371172899</v>
       </c>
       <c r="D77">
-        <v>323.6255333976637</v>
+        <v>320.8896288271009</v>
       </c>
       <c r="E77">
-        <v>27.02499999999998</v>
+        <v>33.22399999999999</v>
       </c>
       <c r="F77">
-        <v>464.925</v>
+        <v>471.124</v>
       </c>
       <c r="G77">
         <v>25.3</v>
@@ -7595,37 +7595,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M77">
-        <v>68.25099</v>
+        <v>69.1610032</v>
       </c>
       <c r="N77">
-        <v>-12.15099000000001</v>
+        <v>-13.0610032</v>
       </c>
       <c r="O77">
-        <v>-3.037747500000002</v>
+        <v>-3.2652508</v>
       </c>
       <c r="P77">
-        <v>-9.113242500000005</v>
+        <v>-9.795752400000001</v>
       </c>
       <c r="Q77">
-        <v>58.7867575</v>
+        <v>58.10424760000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1888410559353275</v>
+        <v>0.1948010999326328</v>
       </c>
       <c r="T77">
-        <v>2.788136422356936</v>
+        <v>2.904308773288475</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2054915247383224</v>
+        <v>0.2027876888865024</v>
       </c>
       <c r="W77">
-        <v>0.1166338441684143</v>
+        <v>0.1170307672714615</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8219660989532898</v>
+        <v>0.8111507555460098</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1356956471101426</v>
+        <v>0.1367056471101426</v>
       </c>
       <c r="C78">
-        <v>-124.934371172899</v>
+        <v>-133.8234052885095</v>
       </c>
       <c r="D78">
-        <v>320.8896288271009</v>
+        <v>318.1995947114905</v>
       </c>
       <c r="E78">
-        <v>33.22399999999999</v>
+        <v>39.423</v>
       </c>
       <c r="F78">
-        <v>471.124</v>
+        <v>477.323</v>
       </c>
       <c r="G78">
         <v>25.3</v>
@@ -7677,37 +7677,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M78">
-        <v>69.1610032</v>
+        <v>70.0710164</v>
       </c>
       <c r="N78">
-        <v>-13.0610032</v>
+        <v>-13.97101640000001</v>
       </c>
       <c r="O78">
-        <v>-3.2652508</v>
+        <v>-3.492754100000003</v>
       </c>
       <c r="P78">
-        <v>-9.795752400000001</v>
+        <v>-10.47826230000001</v>
       </c>
       <c r="Q78">
-        <v>58.10424760000001</v>
+        <v>57.42173769999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1948010999326328</v>
+        <v>0.201279408625356</v>
       </c>
       <c r="T78">
-        <v>2.904308773288475</v>
+        <v>3.030583067779279</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2027876888865024</v>
+        <v>0.2001540825373271</v>
       </c>
       <c r="W78">
-        <v>0.1170307672714615</v>
+        <v>0.1174173806835204</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8111507555460098</v>
+        <v>0.8006163301493082</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1367056471101426</v>
+        <v>0.1815878181275807</v>
       </c>
       <c r="C79">
-        <v>-133.8234052885095</v>
+        <v>-226.3866887608124</v>
       </c>
       <c r="D79">
-        <v>318.1995947114905</v>
+        <v>231.8353112391876</v>
       </c>
       <c r="E79">
-        <v>39.423</v>
+        <v>45.62200000000001</v>
       </c>
       <c r="F79">
-        <v>477.323</v>
+        <v>483.522</v>
       </c>
       <c r="G79">
         <v>25.3</v>
@@ -7759,45 +7759,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M79">
-        <v>70.0710164</v>
+        <v>97.09121760000001</v>
       </c>
       <c r="N79">
-        <v>-13.97101640000001</v>
+        <v>-40.99121760000001</v>
       </c>
       <c r="O79">
-        <v>-3.492754100000003</v>
+        <v>-10.2478044</v>
       </c>
       <c r="P79">
-        <v>-10.47826230000001</v>
+        <v>-30.74341320000001</v>
       </c>
       <c r="Q79">
-        <v>57.42173769999999</v>
+        <v>37.1565868</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.201279408625356</v>
+        <v>0.2163110681875909</v>
       </c>
       <c r="T79">
-        <v>3.030583067779279</v>
+        <v>3.323578091060468</v>
       </c>
       <c r="U79">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.2001540825373271</v>
+        <v>0.1444517881913966</v>
       </c>
       <c r="W79">
-        <v>0.1174173806835204</v>
+        <v>0.1717940809311676</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8006163301493082</v>
+        <v>0.5778071527655864</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1815878181275807</v>
+        <v>0.1831378181275807</v>
       </c>
       <c r="C80">
-        <v>-226.3866887608124</v>
+        <v>-234.7385704668971</v>
       </c>
       <c r="D80">
-        <v>231.8353112391876</v>
+        <v>229.6824295331029</v>
       </c>
       <c r="E80">
-        <v>45.62200000000001</v>
+        <v>51.82100000000003</v>
       </c>
       <c r="F80">
-        <v>483.522</v>
+        <v>489.721</v>
       </c>
       <c r="G80">
         <v>25.3</v>
@@ -7841,37 +7841,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M80">
-        <v>97.09121760000001</v>
+        <v>98.3359768</v>
       </c>
       <c r="N80">
-        <v>-40.99121760000001</v>
+        <v>-42.2359768</v>
       </c>
       <c r="O80">
-        <v>-10.2478044</v>
+        <v>-10.5589942</v>
       </c>
       <c r="P80">
-        <v>-30.74341320000001</v>
+        <v>-31.6769826</v>
       </c>
       <c r="Q80">
-        <v>37.1565868</v>
+        <v>36.2230174</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2163110681875909</v>
+        <v>0.2244306428631905</v>
       </c>
       <c r="T80">
-        <v>3.323578091060468</v>
+        <v>3.4818437144443</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1444517881913966</v>
+        <v>0.1426232845434043</v>
       </c>
       <c r="W80">
-        <v>0.1717940809311676</v>
+        <v>0.1721612444636844</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5778071527655864</v>
+        <v>0.570493138173617</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1831378181275807</v>
+        <v>0.1846878181275807</v>
       </c>
       <c r="C81">
-        <v>-234.7385704668971</v>
+        <v>-243.05083564719</v>
       </c>
       <c r="D81">
-        <v>229.6824295331029</v>
+        <v>227.56916435281</v>
       </c>
       <c r="E81">
-        <v>51.82100000000003</v>
+        <v>58.02000000000004</v>
       </c>
       <c r="F81">
-        <v>489.721</v>
+        <v>495.92</v>
       </c>
       <c r="G81">
         <v>25.3</v>
@@ -7923,37 +7923,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M81">
-        <v>98.3359768</v>
+        <v>99.580736</v>
       </c>
       <c r="N81">
-        <v>-42.2359768</v>
+        <v>-43.48073600000001</v>
       </c>
       <c r="O81">
-        <v>-10.5589942</v>
+        <v>-10.870184</v>
       </c>
       <c r="P81">
-        <v>-31.6769826</v>
+        <v>-32.61055200000001</v>
       </c>
       <c r="Q81">
-        <v>36.2230174</v>
+        <v>35.289448</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2244306428631905</v>
+        <v>0.2333621750063501</v>
       </c>
       <c r="T81">
-        <v>3.4818437144443</v>
+        <v>3.655935900166515</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1426232845434043</v>
+        <v>0.1408404934866117</v>
       </c>
       <c r="W81">
-        <v>0.1721612444636844</v>
+        <v>0.1725192289078884</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.570493138173617</v>
+        <v>0.5633619739464468</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1846878181275807</v>
+        <v>0.1862378181275807</v>
       </c>
       <c r="C82">
-        <v>-243.05083564719</v>
+        <v>-251.3245678449981</v>
       </c>
       <c r="D82">
-        <v>227.56916435281</v>
+        <v>225.4944321550019</v>
       </c>
       <c r="E82">
-        <v>58.02000000000004</v>
+        <v>64.21900000000005</v>
       </c>
       <c r="F82">
-        <v>495.92</v>
+        <v>502.119</v>
       </c>
       <c r="G82">
         <v>25.3</v>
@@ -8005,37 +8005,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M82">
-        <v>99.580736</v>
+        <v>100.8254952</v>
       </c>
       <c r="N82">
-        <v>-43.48073600000001</v>
+        <v>-44.72549520000001</v>
       </c>
       <c r="O82">
-        <v>-10.870184</v>
+        <v>-11.1813738</v>
       </c>
       <c r="P82">
-        <v>-32.61055200000001</v>
+        <v>-33.54412140000001</v>
       </c>
       <c r="Q82">
-        <v>35.289448</v>
+        <v>34.3558786</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2333621750063501</v>
+        <v>0.2432338684277369</v>
       </c>
       <c r="T82">
-        <v>3.655935900166515</v>
+        <v>3.848353579122648</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1408404934866117</v>
+        <v>0.1391017219620856</v>
       </c>
       <c r="W82">
-        <v>0.1725192289078884</v>
+        <v>0.1728683742300132</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5633619739464468</v>
+        <v>0.5564068878483425</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1862378181275807</v>
+        <v>0.1877878181275807</v>
       </c>
       <c r="C83">
-        <v>-251.3245678449981</v>
+        <v>-259.5608114462679</v>
       </c>
       <c r="D83">
-        <v>225.4944321550019</v>
+        <v>223.4571885537321</v>
       </c>
       <c r="E83">
-        <v>64.21900000000005</v>
+        <v>70.41800000000006</v>
       </c>
       <c r="F83">
-        <v>502.119</v>
+        <v>508.318</v>
       </c>
       <c r="G83">
         <v>25.3</v>
@@ -8087,37 +8087,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M83">
-        <v>100.8254952</v>
+        <v>102.0702544</v>
       </c>
       <c r="N83">
-        <v>-44.72549520000001</v>
+        <v>-45.97025440000002</v>
       </c>
       <c r="O83">
-        <v>-11.1813738</v>
+        <v>-11.4925636</v>
       </c>
       <c r="P83">
-        <v>-33.54412140000001</v>
+        <v>-34.47769080000001</v>
       </c>
       <c r="Q83">
-        <v>34.3558786</v>
+        <v>33.42230919999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2432338684277369</v>
+        <v>0.2542024166737223</v>
       </c>
       <c r="T83">
-        <v>3.848353579122648</v>
+        <v>4.062151000185017</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1391017219620856</v>
+        <v>0.1374053594991334</v>
       </c>
       <c r="W83">
-        <v>0.1728683742300132</v>
+        <v>0.173209003812574</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5564068878483425</v>
+        <v>0.5496214379965334</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1877878181275807</v>
+        <v>0.1893378181275807</v>
       </c>
       <c r="C84">
-        <v>-259.5608114462679</v>
+        <v>-267.7605734325967</v>
       </c>
       <c r="D84">
-        <v>223.4571885537321</v>
+        <v>221.4564265674033</v>
       </c>
       <c r="E84">
-        <v>70.41800000000006</v>
+        <v>76.61700000000008</v>
       </c>
       <c r="F84">
-        <v>508.318</v>
+        <v>514.5170000000001</v>
       </c>
       <c r="G84">
         <v>25.3</v>
@@ -8169,37 +8169,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M84">
-        <v>102.0702544</v>
+        <v>103.3150136</v>
       </c>
       <c r="N84">
-        <v>-45.97025440000002</v>
+        <v>-47.21501360000002</v>
       </c>
       <c r="O84">
-        <v>-11.4925636</v>
+        <v>-11.80375340000001</v>
       </c>
       <c r="P84">
-        <v>-34.47769080000001</v>
+        <v>-35.41126020000002</v>
       </c>
       <c r="Q84">
-        <v>33.42230919999999</v>
+        <v>32.48873979999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2542024166737223</v>
+        <v>0.2664613823604118</v>
       </c>
       <c r="T84">
-        <v>4.062151000185017</v>
+        <v>4.30110105901943</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1374053594991334</v>
+        <v>0.1357498732401076</v>
       </c>
       <c r="W84">
-        <v>0.173209003812574</v>
+        <v>0.1735414254533864</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5496214379965334</v>
+        <v>0.5429994929604305</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1893378181275807</v>
+        <v>0.1908878181275807</v>
       </c>
       <c r="C85">
-        <v>-267.7605734325967</v>
+        <v>-275.9248250409029</v>
       </c>
       <c r="D85">
-        <v>221.4564265674033</v>
+        <v>219.4911749590972</v>
       </c>
       <c r="E85">
-        <v>76.61700000000008</v>
+        <v>82.81600000000003</v>
       </c>
       <c r="F85">
-        <v>514.5170000000001</v>
+        <v>520.716</v>
       </c>
       <c r="G85">
         <v>25.3</v>
@@ -8251,37 +8251,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M85">
-        <v>103.3150136</v>
+        <v>104.5597728</v>
       </c>
       <c r="N85">
-        <v>-47.21501360000002</v>
+        <v>-48.45977280000001</v>
       </c>
       <c r="O85">
-        <v>-11.80375340000001</v>
+        <v>-12.1149432</v>
       </c>
       <c r="P85">
-        <v>-35.41126020000002</v>
+        <v>-36.34482960000001</v>
       </c>
       <c r="Q85">
-        <v>32.48873979999999</v>
+        <v>31.55517039999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2664613823604118</v>
+        <v>0.2802527187579377</v>
       </c>
       <c r="T85">
-        <v>4.30110105901943</v>
+        <v>4.569919875208146</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1357498732401076</v>
+        <v>0.1341338033205826</v>
       </c>
       <c r="W85">
-        <v>0.1735414254533864</v>
+        <v>0.173865932293227</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5429994929604305</v>
+        <v>0.5365352132823302</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1908878181275807</v>
+        <v>0.1924378181275807</v>
       </c>
       <c r="C86">
-        <v>-275.9248250409029</v>
+        <v>-284.0545033355048</v>
       </c>
       <c r="D86">
-        <v>219.4911749590972</v>
+        <v>217.5604966644952</v>
       </c>
       <c r="E86">
-        <v>82.81600000000003</v>
+        <v>89.01499999999999</v>
       </c>
       <c r="F86">
-        <v>520.716</v>
+        <v>526.915</v>
       </c>
       <c r="G86">
         <v>25.3</v>
@@ -8333,37 +8333,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M86">
-        <v>104.5597728</v>
+        <v>105.804532</v>
       </c>
       <c r="N86">
-        <v>-48.45977280000001</v>
+        <v>-49.704532</v>
       </c>
       <c r="O86">
-        <v>-12.1149432</v>
+        <v>-12.426133</v>
       </c>
       <c r="P86">
-        <v>-36.34482960000001</v>
+        <v>-37.278399</v>
       </c>
       <c r="Q86">
-        <v>31.55517039999999</v>
+        <v>30.62160100000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2802527187579375</v>
+        <v>0.2958829000084667</v>
       </c>
       <c r="T86">
-        <v>4.569919875208143</v>
+        <v>4.874581200222019</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1341338033205826</v>
+        <v>0.1325557585756345</v>
       </c>
       <c r="W86">
-        <v>0.173865932293227</v>
+        <v>0.1741828036780126</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5365352132823302</v>
+        <v>0.5302230343025381</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1924378181275807</v>
+        <v>0.1939878181275807</v>
       </c>
       <c r="C87">
-        <v>-284.0545033355048</v>
+        <v>-292.1505126979532</v>
       </c>
       <c r="D87">
-        <v>217.5604966644952</v>
+        <v>215.6634873020467</v>
       </c>
       <c r="E87">
-        <v>89.01499999999999</v>
+        <v>95.21399999999994</v>
       </c>
       <c r="F87">
-        <v>526.915</v>
+        <v>533.1139999999999</v>
       </c>
       <c r="G87">
         <v>25.3</v>
@@ -8415,37 +8415,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M87">
-        <v>105.804532</v>
+        <v>107.0492912</v>
       </c>
       <c r="N87">
-        <v>-49.704532</v>
+        <v>-50.94929119999999</v>
       </c>
       <c r="O87">
-        <v>-12.426133</v>
+        <v>-12.7373228</v>
       </c>
       <c r="P87">
-        <v>-37.278399</v>
+        <v>-38.21196839999999</v>
       </c>
       <c r="Q87">
-        <v>30.62160100000001</v>
+        <v>29.68803160000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2958829000084667</v>
+        <v>0.3137459642947857</v>
       </c>
       <c r="T87">
-        <v>4.874581200222019</v>
+        <v>5.222765571666448</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1325557585756345</v>
+        <v>0.1310144125456853</v>
       </c>
       <c r="W87">
-        <v>0.1741828036780126</v>
+        <v>0.1744923059608264</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5302230343025381</v>
+        <v>0.5240576501827412</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1939878181275807</v>
+        <v>0.1955378181275807</v>
       </c>
       <c r="C88">
-        <v>-292.1505126979532</v>
+        <v>-300.2137262395946</v>
       </c>
       <c r="D88">
-        <v>215.6634873020467</v>
+        <v>213.7992737604053</v>
       </c>
       <c r="E88">
-        <v>95.21399999999994</v>
+        <v>101.413</v>
       </c>
       <c r="F88">
-        <v>533.1139999999999</v>
+        <v>539.313</v>
       </c>
       <c r="G88">
         <v>25.3</v>
@@ -8497,37 +8497,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M88">
-        <v>107.0492912</v>
+        <v>108.2940504</v>
       </c>
       <c r="N88">
-        <v>-50.94929119999999</v>
+        <v>-52.19405040000001</v>
       </c>
       <c r="O88">
-        <v>-12.7373228</v>
+        <v>-13.0485126</v>
       </c>
       <c r="P88">
-        <v>-38.21196839999999</v>
+        <v>-39.14553780000001</v>
       </c>
       <c r="Q88">
-        <v>29.68803160000002</v>
+        <v>28.7544622</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3137459642947857</v>
+        <v>0.3343571923174616</v>
       </c>
       <c r="T88">
-        <v>5.222765571666448</v>
+        <v>5.624516769486945</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1310144125456853</v>
+        <v>0.1295084997578038</v>
       </c>
       <c r="W88">
-        <v>0.1744923059608264</v>
+        <v>0.174794693248633</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5240576501827412</v>
+        <v>0.5180339990312154</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1955378181275807</v>
+        <v>0.1970878181275807</v>
       </c>
       <c r="C89">
-        <v>-300.2137262395946</v>
+        <v>-308.2449871414998</v>
       </c>
       <c r="D89">
-        <v>213.7992737604053</v>
+        <v>211.9670128585001</v>
       </c>
       <c r="E89">
-        <v>101.413</v>
+        <v>107.612</v>
       </c>
       <c r="F89">
-        <v>539.313</v>
+        <v>545.5119999999999</v>
       </c>
       <c r="G89">
         <v>25.3</v>
@@ -8579,37 +8579,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M89">
-        <v>108.2940504</v>
+        <v>109.5388096</v>
       </c>
       <c r="N89">
-        <v>-52.19405040000001</v>
+        <v>-53.4388096</v>
       </c>
       <c r="O89">
-        <v>-13.0485126</v>
+        <v>-13.3597024</v>
       </c>
       <c r="P89">
-        <v>-39.14553780000001</v>
+        <v>-40.0791072</v>
       </c>
       <c r="Q89">
-        <v>28.7544622</v>
+        <v>27.82089280000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3343571923174616</v>
+        <v>0.3584036250105834</v>
       </c>
       <c r="T89">
-        <v>5.624516769486945</v>
+        <v>6.093226500277525</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1295084997578038</v>
+        <v>0.1280368122605561</v>
       </c>
       <c r="W89">
-        <v>0.174794693248633</v>
+        <v>0.1750902080980803</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5180339990312154</v>
+        <v>0.5121472490422243</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1970878181275807</v>
+        <v>0.1986378181275807</v>
       </c>
       <c r="C90">
-        <v>-308.2449871414998</v>
+        <v>-316.2451099260801</v>
       </c>
       <c r="D90">
-        <v>211.9670128585001</v>
+        <v>210.1658900739199</v>
       </c>
       <c r="E90">
-        <v>107.612</v>
+        <v>113.811</v>
       </c>
       <c r="F90">
-        <v>545.5119999999999</v>
+        <v>551.711</v>
       </c>
       <c r="G90">
         <v>25.3</v>
@@ -8661,37 +8661,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M90">
-        <v>109.5388096</v>
+        <v>110.7835688</v>
       </c>
       <c r="N90">
-        <v>-53.4388096</v>
+        <v>-54.68356880000002</v>
       </c>
       <c r="O90">
-        <v>-13.3597024</v>
+        <v>-13.6708922</v>
       </c>
       <c r="P90">
-        <v>-40.0791072</v>
+        <v>-41.01267660000001</v>
       </c>
       <c r="Q90">
-        <v>27.82089280000001</v>
+        <v>26.88732339999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3584036250105834</v>
+        <v>0.3868221363751818</v>
       </c>
       <c r="T90">
-        <v>6.093226500277525</v>
+        <v>6.647156182120935</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1280368122605561</v>
+        <v>0.1265981963924599</v>
       </c>
       <c r="W90">
-        <v>0.1750902080980803</v>
+        <v>0.175379082164394</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5121472490422243</v>
+        <v>0.5063927855698398</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1986378181275807</v>
+        <v>0.2001878181275807</v>
       </c>
       <c r="C91">
-        <v>-316.2451099260801</v>
+        <v>-324.2148816644168</v>
       </c>
       <c r="D91">
-        <v>210.1658900739199</v>
+        <v>208.3951183355831</v>
       </c>
       <c r="E91">
-        <v>113.811</v>
+        <v>120.01</v>
       </c>
       <c r="F91">
-        <v>551.711</v>
+        <v>557.91</v>
       </c>
       <c r="G91">
         <v>25.3</v>
@@ -8743,37 +8743,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M91">
-        <v>110.7835688</v>
+        <v>112.028328</v>
       </c>
       <c r="N91">
-        <v>-54.68356880000002</v>
+        <v>-55.92832800000001</v>
       </c>
       <c r="O91">
-        <v>-13.6708922</v>
+        <v>-13.982082</v>
       </c>
       <c r="P91">
-        <v>-41.01267660000001</v>
+        <v>-41.946246</v>
       </c>
       <c r="Q91">
-        <v>26.88732339999999</v>
+        <v>25.953754</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3868221363751818</v>
+        <v>0.4209243500127001</v>
       </c>
       <c r="T91">
-        <v>6.647156182120935</v>
+        <v>7.311871800333031</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1265981963924599</v>
+        <v>0.1251915497658771</v>
       </c>
       <c r="W91">
-        <v>0.175379082164394</v>
+        <v>0.1756615368070119</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5063927855698398</v>
+        <v>0.5007661990635082</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2001878181275807</v>
+        <v>0.2342948402969959</v>
       </c>
       <c r="C92">
-        <v>-324.2148816644168</v>
+        <v>-363.0076555225943</v>
       </c>
       <c r="D92">
-        <v>208.3951183355831</v>
+        <v>175.8013444774058</v>
       </c>
       <c r="E92">
-        <v>120.01</v>
+        <v>126.2090000000001</v>
       </c>
       <c r="F92">
-        <v>557.91</v>
+        <v>564.109</v>
       </c>
       <c r="G92">
         <v>25.3</v>
@@ -8825,45 +8825,45 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M92">
-        <v>112.028328</v>
+        <v>133.0169022</v>
       </c>
       <c r="N92">
-        <v>-55.92832800000001</v>
+        <v>-76.91690220000001</v>
       </c>
       <c r="O92">
-        <v>-13.982082</v>
+        <v>-19.22922555</v>
       </c>
       <c r="P92">
-        <v>-41.946246</v>
+        <v>-57.68767665000001</v>
       </c>
       <c r="Q92">
-        <v>25.953754</v>
+        <v>10.21232335</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4209243500127001</v>
+        <v>0.4704606352298353</v>
       </c>
       <c r="T92">
-        <v>7.311871800333031</v>
+        <v>8.277426201054183</v>
       </c>
       <c r="U92">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1251915497658771</v>
+        <v>0.1054377283490819</v>
       </c>
       <c r="W92">
-        <v>0.1756615368070119</v>
+        <v>0.2109377836552865</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.5007661990635082</v>
+        <v>0.4217509133963278</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2342948402969959</v>
+        <v>0.2361948402969959</v>
       </c>
       <c r="C93">
-        <v>-363.0076555225943</v>
+        <v>-370.7251442478476</v>
       </c>
       <c r="D93">
-        <v>175.8013444774058</v>
+        <v>174.2828557521524</v>
       </c>
       <c r="E93">
-        <v>126.2090000000001</v>
+        <v>132.408</v>
       </c>
       <c r="F93">
-        <v>564.109</v>
+        <v>570.308</v>
       </c>
       <c r="G93">
         <v>25.3</v>
@@ -8907,37 +8907,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M93">
-        <v>133.0169022</v>
+        <v>134.4786264</v>
       </c>
       <c r="N93">
-        <v>-76.91690220000001</v>
+        <v>-78.3786264</v>
       </c>
       <c r="O93">
-        <v>-19.22922555</v>
+        <v>-19.5946566</v>
       </c>
       <c r="P93">
-        <v>-57.68767665000001</v>
+        <v>-58.7839698</v>
       </c>
       <c r="Q93">
-        <v>10.21232335</v>
+        <v>9.116030200000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4704606352298353</v>
+        <v>0.5235432146335648</v>
       </c>
       <c r="T93">
-        <v>8.277426201054183</v>
+        <v>9.312104476185958</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1054377283490819</v>
+        <v>0.104291666084418</v>
       </c>
       <c r="W93">
-        <v>0.2109377836552865</v>
+        <v>0.2112080251372943</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4217509133963278</v>
+        <v>0.417166664337672</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2361948402969959</v>
+        <v>0.2380948402969959</v>
       </c>
       <c r="C94">
-        <v>-370.7251442478476</v>
+        <v>-378.4166256397185</v>
       </c>
       <c r="D94">
-        <v>174.2828557521524</v>
+        <v>172.7903743602815</v>
       </c>
       <c r="E94">
-        <v>132.408</v>
+        <v>138.6070000000001</v>
       </c>
       <c r="F94">
-        <v>570.308</v>
+        <v>576.5070000000001</v>
       </c>
       <c r="G94">
         <v>25.3</v>
@@ -8989,37 +8989,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M94">
-        <v>134.4786264</v>
+        <v>135.9403506</v>
       </c>
       <c r="N94">
-        <v>-78.3786264</v>
+        <v>-79.84035060000002</v>
       </c>
       <c r="O94">
-        <v>-19.5946566</v>
+        <v>-19.96008765000001</v>
       </c>
       <c r="P94">
-        <v>-58.7839698</v>
+        <v>-59.88026295000002</v>
       </c>
       <c r="Q94">
-        <v>9.116030200000004</v>
+        <v>8.019737049999989</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5235432146335648</v>
+        <v>0.5917922452955027</v>
       </c>
       <c r="T94">
-        <v>9.312104476185958</v>
+        <v>10.6424051156411</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.104291666084418</v>
+        <v>0.1031702503200694</v>
       </c>
       <c r="W94">
-        <v>0.2112080251372943</v>
+        <v>0.2114724549745276</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.417166664337672</v>
+        <v>0.4126810012802776</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2380948402969959</v>
+        <v>0.2399948402969959</v>
       </c>
       <c r="C95">
-        <v>-378.4166256397185</v>
+        <v>-386.0827621710273</v>
       </c>
       <c r="D95">
-        <v>172.7903743602815</v>
+        <v>171.3232378289727</v>
       </c>
       <c r="E95">
-        <v>138.6070000000001</v>
+        <v>144.806</v>
       </c>
       <c r="F95">
-        <v>576.5070000000001</v>
+        <v>582.706</v>
       </c>
       <c r="G95">
         <v>25.3</v>
@@ -9071,37 +9071,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M95">
-        <v>135.9403506</v>
+        <v>137.4020748</v>
       </c>
       <c r="N95">
-        <v>-79.84035060000002</v>
+        <v>-81.30207480000001</v>
       </c>
       <c r="O95">
-        <v>-19.96008765000001</v>
+        <v>-20.3255187</v>
       </c>
       <c r="P95">
-        <v>-59.88026295000002</v>
+        <v>-60.97655610000001</v>
       </c>
       <c r="Q95">
-        <v>8.019737049999989</v>
+        <v>6.923443899999995</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5917922452955027</v>
+        <v>0.6827909528447532</v>
       </c>
       <c r="T95">
-        <v>10.6424051156411</v>
+        <v>12.41613930158128</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1031702503200694</v>
+        <v>0.1020726944656006</v>
       </c>
       <c r="W95">
-        <v>0.2114724549745276</v>
+        <v>0.2117312586450114</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4126810012802776</v>
+        <v>0.4082907778624023</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2399948402969959</v>
+        <v>0.2418948402969959</v>
       </c>
       <c r="C96">
-        <v>-386.0827621710273</v>
+        <v>-393.7241940042087</v>
       </c>
       <c r="D96">
-        <v>171.3232378289727</v>
+        <v>169.8808059957913</v>
       </c>
       <c r="E96">
-        <v>144.806</v>
+        <v>151.005</v>
       </c>
       <c r="F96">
-        <v>582.706</v>
+        <v>588.905</v>
       </c>
       <c r="G96">
         <v>25.3</v>
@@ -9153,37 +9153,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M96">
-        <v>137.4020748</v>
+        <v>138.863799</v>
       </c>
       <c r="N96">
-        <v>-81.30207480000001</v>
+        <v>-82.76379900000001</v>
       </c>
       <c r="O96">
-        <v>-20.3255187</v>
+        <v>-20.69094975</v>
       </c>
       <c r="P96">
-        <v>-60.97655610000001</v>
+        <v>-62.07284925</v>
       </c>
       <c r="Q96">
-        <v>6.923443899999995</v>
+        <v>5.827150750000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6827909528447532</v>
+        <v>0.8101891434137043</v>
       </c>
       <c r="T96">
-        <v>12.41613930158128</v>
+        <v>14.89936716189755</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1020726944656006</v>
+        <v>0.1009982450501732</v>
       </c>
       <c r="W96">
-        <v>0.2117312586450114</v>
+        <v>0.2119846138171692</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4082907778624023</v>
+        <v>0.4039929802006929</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2418948402969959</v>
+        <v>0.2437948402969959</v>
       </c>
       <c r="C97">
-        <v>-393.7241940042087</v>
+        <v>-401.341539922666</v>
       </c>
       <c r="D97">
-        <v>169.8808059957913</v>
+        <v>168.462460077334</v>
       </c>
       <c r="E97">
-        <v>151.005</v>
+        <v>157.2040000000001</v>
       </c>
       <c r="F97">
-        <v>588.905</v>
+        <v>595.104</v>
       </c>
       <c r="G97">
         <v>25.3</v>
@@ -9235,37 +9235,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M97">
-        <v>138.863799</v>
+        <v>140.3255232</v>
       </c>
       <c r="N97">
-        <v>-82.76379900000001</v>
+        <v>-84.22552320000003</v>
       </c>
       <c r="O97">
-        <v>-20.69094975</v>
+        <v>-21.05638080000001</v>
       </c>
       <c r="P97">
-        <v>-62.07284925</v>
+        <v>-63.16914240000002</v>
       </c>
       <c r="Q97">
-        <v>5.827150750000001</v>
+        <v>4.730857599999986</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8101891434137043</v>
+        <v>1.001286429267131</v>
       </c>
       <c r="T97">
-        <v>14.89936716189755</v>
+        <v>18.62420895237194</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1009982450501732</v>
+        <v>0.09994617999756723</v>
       </c>
       <c r="W97">
-        <v>0.2119846138171692</v>
+        <v>0.2122326907565736</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4039929802006929</v>
+        <v>0.3997847199902689</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2437948402969959</v>
+        <v>0.2456948402969959</v>
       </c>
       <c r="C98">
-        <v>-401.3415399226659</v>
+        <v>-408.9353982158557</v>
       </c>
       <c r="D98">
-        <v>168.462460077334</v>
+        <v>167.0676017841443</v>
       </c>
       <c r="E98">
-        <v>157.204</v>
+        <v>163.403</v>
       </c>
       <c r="F98">
-        <v>595.1039999999999</v>
+        <v>601.303</v>
       </c>
       <c r="G98">
         <v>25.3</v>
@@ -9317,37 +9317,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M98">
-        <v>140.3255232</v>
+        <v>141.7872474</v>
       </c>
       <c r="N98">
-        <v>-84.2255232</v>
+        <v>-85.68724740000002</v>
       </c>
       <c r="O98">
-        <v>-21.0563808</v>
+        <v>-21.42181185</v>
       </c>
       <c r="P98">
-        <v>-63.1691424</v>
+        <v>-64.26543555000001</v>
       </c>
       <c r="Q98">
-        <v>4.730857600000007</v>
+        <v>3.634564449999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.001286429267128</v>
+        <v>1.319781905689504</v>
       </c>
       <c r="T98">
-        <v>18.62420895237189</v>
+        <v>24.83227860316252</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09994617999756725</v>
+        <v>0.09891580700790159</v>
       </c>
       <c r="W98">
-        <v>0.2122326907565736</v>
+        <v>0.2124756527075368</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.399784719990269</v>
+        <v>0.3956632280316064</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2456948402969959</v>
+        <v>0.2475948402969959</v>
       </c>
       <c r="C99">
-        <v>-408.9353982158557</v>
+        <v>-416.5063475207634</v>
       </c>
       <c r="D99">
-        <v>167.0676017841443</v>
+        <v>165.6956524792366</v>
       </c>
       <c r="E99">
-        <v>163.403</v>
+        <v>169.602</v>
       </c>
       <c r="F99">
-        <v>601.303</v>
+        <v>607.502</v>
       </c>
       <c r="G99">
         <v>25.3</v>
@@ -9399,37 +9399,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M99">
-        <v>141.7872474</v>
+        <v>143.2489716</v>
       </c>
       <c r="N99">
-        <v>-85.68724740000002</v>
+        <v>-87.14897160000001</v>
       </c>
       <c r="O99">
-        <v>-21.42181185</v>
+        <v>-21.7872429</v>
       </c>
       <c r="P99">
-        <v>-64.26543555000001</v>
+        <v>-65.36172870000001</v>
       </c>
       <c r="Q99">
-        <v>3.634564449999999</v>
+        <v>2.538271299999991</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.319781905689504</v>
+        <v>1.956772858534257</v>
       </c>
       <c r="T99">
-        <v>24.83227860316252</v>
+        <v>37.24841790474378</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09891580700790159</v>
+        <v>0.09790646203843321</v>
       </c>
       <c r="W99">
-        <v>0.2124756527075368</v>
+        <v>0.2127136562513375</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3956632280316064</v>
+        <v>0.3916258481537329</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2475948402969959</v>
+        <v>0.2494948402969958</v>
       </c>
       <c r="C100">
-        <v>-416.5063475207634</v>
+        <v>-424.0549476222558</v>
       </c>
       <c r="D100">
-        <v>165.6956524792366</v>
+        <v>164.3460523777442</v>
       </c>
       <c r="E100">
-        <v>169.602</v>
+        <v>175.801</v>
       </c>
       <c r="F100">
-        <v>607.502</v>
+        <v>613.701</v>
       </c>
       <c r="G100">
         <v>25.3</v>
@@ -9481,37 +9481,37 @@
         <v>56.09999999999999</v>
       </c>
       <c r="M100">
-        <v>143.2489716</v>
+        <v>144.7106958</v>
       </c>
       <c r="N100">
-        <v>-87.14897160000001</v>
+        <v>-88.61069580000003</v>
       </c>
       <c r="O100">
-        <v>-21.7872429</v>
+        <v>-22.15267395000001</v>
       </c>
       <c r="P100">
-        <v>-65.36172870000001</v>
+        <v>-66.45802185000002</v>
       </c>
       <c r="Q100">
-        <v>2.538271299999991</v>
+        <v>1.441978149999983</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.956772858534257</v>
+        <v>3.867745717068513</v>
       </c>
       <c r="T100">
-        <v>37.24841790474378</v>
+        <v>74.49683580948756</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09790646203843321</v>
+        <v>0.09691750787642883</v>
       </c>
       <c r="W100">
-        <v>0.2127136562513375</v>
+        <v>0.2129468516427381</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3916258481537329</v>
+        <v>0.3876700315057153</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2494948402969958</v>
-      </c>
-      <c r="C101">
-        <v>-424.0549476222558</v>
-      </c>
-      <c r="D101">
-        <v>164.3460523777442</v>
-      </c>
-      <c r="E101">
-        <v>175.801</v>
-      </c>
-      <c r="F101">
-        <v>613.701</v>
-      </c>
-      <c r="G101">
-        <v>25.3</v>
-      </c>
-      <c r="H101">
-        <v>182</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>124</v>
-      </c>
-      <c r="K101">
-        <v>67.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>56.09999999999999</v>
-      </c>
-      <c r="M101">
-        <v>144.7106958</v>
-      </c>
-      <c r="N101">
-        <v>-88.61069580000003</v>
-      </c>
-      <c r="O101">
-        <v>-22.15267395000001</v>
-      </c>
-      <c r="P101">
-        <v>-66.45802185000002</v>
-      </c>
-      <c r="Q101">
-        <v>1.441978149999983</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.867745717068513</v>
-      </c>
-      <c r="T101">
-        <v>74.49683580948756</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09691750787642883</v>
-      </c>
-      <c r="W101">
-        <v>0.2129468516427381</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3876700315057153</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
